--- a/data/trending_integrated_20260911_14.xlsx
+++ b/data/trending_integrated_20260911_14.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>비엘팜텍</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2720</v>
+        <v>16060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.83%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.04</v>
+        <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="G2" t="n">
-        <v>342</v>
+        <v>157</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
+        <v>2.39</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2095</v>
+        <v>12610</v>
       </c>
       <c r="K2" t="n">
-        <v>2090</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.36</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>8076180404</v>
+        <v>208118000000</v>
       </c>
       <c r="P2" t="n">
-        <v>8150</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>220000</v>
+        <v>-71000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
+          <t>AI 다음 핵심 시장으로 사이버 보안 부문 지목. 젠슨 황 발언에 따른 보안 섹터 급등 및 엑스게이트 수혜 전망. 594억 공급계약 및 모건스텐리 매집 호재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
+          <t>['사이버 보안', '젠슨 황', '공급계약']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,43 +643,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>065170</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16060</v>
+        <v>2720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.36%</t>
+          <t>+25.93%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.22</v>
+        <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>155</v>
+        <v>355</v>
       </c>
       <c r="H3" t="n">
-        <v>2.39</v>
+        <v>1.32</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12610</v>
+        <v>2160</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>1.36</v>
       </c>
       <c r="O3" t="n">
-        <v>208073000000</v>
+        <v>8080000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -711,23 +711,23 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-71000</v>
+        <v>220000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 다음 핵심 시장으로 사이버 보안 부문 지목. 젠슨 황 발언에 따른 보안 섹터 급등 및 엑스게이트 수혜 전망. 594억 공급계약 및 모건스텐리 매집 호재.</t>
+          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['사이버 보안', '젠슨 황', '공급계약']</t>
+          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>065170</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15230</v>
+        <v>2630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+25.97%</t>
+          <t>+23.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>439</v>
+        <v>116</v>
       </c>
       <c r="F4" t="n">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>951</v>
+        <v>163</v>
       </c>
       <c r="H4" t="n">
-        <v>3.14</v>
+        <v>3.83</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,99 +779,99 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12090</v>
+        <v>2125</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2692</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>204227000000</v>
+        <v>107962739110</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R4" t="n">
-        <v>-386000</v>
+        <v>-2091000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
+          <t>594억 공급 계약 및 모건스탠리 48만주 매집 공시 확인. 미국 정부 양자컴퓨터 보조금 지원 관련 기대감. 거래량 증가와 함께 손바뀜 가능성 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁 테마', 'WTI']</t>
+          <t>['공급계약', '양자컴퓨터', '매집공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16740</v>
+        <v>14960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+25.49%</t>
+          <t>+23.74%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.19</v>
+        <v>3.11</v>
       </c>
       <c r="E5" t="n">
-        <v>106</v>
+        <v>448</v>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>253</v>
       </c>
       <c r="G5" t="n">
-        <v>163</v>
+        <v>958</v>
       </c>
       <c r="H5" t="n">
-        <v>1.24</v>
+        <v>3.14</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13340</v>
+        <v>12090</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.43</v>
+        <v>0.03</v>
       </c>
       <c r="O5" t="n">
-        <v>148622000000</v>
+        <v>205865000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,106 +895,106 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>36000</v>
+        <v>-386000</v>
       </c>
       <c r="S5" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>K-뷰티 대장주로서의 기대감과 함께 급등세 지속 전망. 경영권 이슈 및 전고점 돌파 기대감 반영. 알바 언급 및 매수세 유입 추측.</t>
+          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['K-뷰티', '대장주', '경영권']</t>
+          <t>['국제유가', '전쟁 테마', 'WTI']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2590</v>
+        <v>16450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+21.88%</t>
+          <t>+23.31%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="E6" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H6" t="n">
-        <v>3.83</v>
+        <v>1.24</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2125</v>
+        <v>13340</v>
       </c>
       <c r="K6" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2692</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.76</v>
+        <v>1.43</v>
       </c>
       <c r="O6" t="n">
-        <v>103156280530</v>
+        <v>154108000000</v>
       </c>
       <c r="P6" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-2091000</v>
+        <v>36000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>594억 공급 계약 및 모건스탠리 48만주 매집 공시 확인. 미국 정부 양자컴퓨터 보조금 지원 관련 기대감. 거래량 증가와 함께 손바뀜 가능성 제기.</t>
+          <t>K-뷰티 대장주로서의 기대감과 함께 급등세 지속 전망. 경영권 이슈 및 전고점 돌파 기대감 반영. 알바 언급 및 매수세 유입 추측.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공급계약', '양자컴퓨터', '매집공시']</t>
+          <t>['K-뷰티', '대장주', '경영권']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>136200</v>
+        <v>136100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+17.72%</t>
+          <t>+17.02%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.26</v>
       </c>
       <c r="E7" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F7" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G7" t="n">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="H7" t="n">
         <v>4.32</v>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>115700</v>
+        <v>116300</v>
       </c>
       <c r="K7" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>4.58</v>
       </c>
       <c r="O7" t="n">
-        <v>479307876900</v>
+        <v>483812000000</v>
       </c>
       <c r="P7" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>물량 부족 및 견조한 차트 패턴에 대한 기대감. 단기 차익 실현 욕구와 함께 밸류에이션에 대한 언급.</t>
+          <t>매출 호조 및 상승 기대감이 있으나, 구체적인 거래량이나 상승 이유에 대한 명확한 분석은 부족함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['단기 매매', '밸류에이션', '수급']</t>
+          <t>['거래량', '상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7290</v>
+        <v>7340</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.96%</t>
+          <t>+11.72%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.79</v>
       </c>
       <c r="E8" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="H8" t="n">
         <v>2.15</v>
@@ -1162,7 +1162,7 @@
         <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>162757000000</v>
+        <v>165038000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1207,39 +1207,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1905</v>
+        <v>7740</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.24%</t>
+          <t>+4.31%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>244</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="G9" t="n">
-        <v>247</v>
+        <v>1136</v>
       </c>
       <c r="H9" t="n">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1760</v>
+        <v>7420</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.17</v>
       </c>
       <c r="O9" t="n">
-        <v>42534000000</v>
+        <v>29479000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1263,27 +1263,27 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-389000</v>
+        <v>-73000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 급등으로 인한 전쟁 테마주 부각. VLCC 용선료 폭등과 같은 단기 호재로 인한 상승 기대감 형성.</t>
+          <t>세계폐암학회(WCLC) 데이터 발표를 통한 주가 대폭등이 예고되었으며, 임상 시험 디자인이 언급됨.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '유가', 'VLCC']</t>
+          <t>['임상 시험', 'WCLC']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,46 +1292,46 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7680</v>
+        <v>3920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>463</v>
+        <v>200</v>
       </c>
       <c r="H10" t="n">
-        <v>11.72</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7100</v>
+        <v>3810</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>11.62</v>
+        <v>1.57</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>93475000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1355,75 +1355,75 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>51000</v>
+        <v>-582000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>광주 반도체 관련 기사 및 신영증권 창구 매수세 유입 관측. 주가 상승 기대감 존재.</t>
+          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '신영증권', '주가상승']</t>
+          <t>['6G통신', '광통신', '데이터센터']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7730</v>
+        <v>19730</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.18%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>234</v>
+        <v>143</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G11" t="n">
-        <v>1104</v>
+        <v>542</v>
       </c>
       <c r="H11" t="n">
-        <v>1.29</v>
+        <v>10.65</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7420</v>
+        <v>19450</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.17</v>
+        <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>28996000000</v>
+        <v>113121000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1447,27 +1447,27 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-73000</v>
+        <v>-76000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>WCLC 학회 센딥파텔 교수 발표에 따른 주가 대폭등 기대. 외국계 증권사 유입 확인.</t>
+          <t>대차해지 관련 주주 독려와 목표가 상향 뉴스가 언급되었으나, 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['WCLC', '임상 시험', '기술 수출']</t>
+          <t>['대차해지', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3915</v>
+        <v>52400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.53</v>
+        <v>-0.44</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3810</v>
+        <v>51800</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>51300</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>54500</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>51300</v>
       </c>
       <c r="N12" t="n">
-        <v>1.57</v>
+        <v>3.36</v>
       </c>
       <c r="O12" t="n">
-        <v>92914000000</v>
+        <v>100140770400</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>87700</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>17210</v>
       </c>
       <c r="R12" t="n">
-        <v>-582000</v>
+        <v>128000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['6G통신', '광통신', '데이터센터']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26400</v>
+        <v>253000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.15%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>-0.96</v>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>236</v>
       </c>
       <c r="F13" t="n">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="G13" t="n">
-        <v>493</v>
+        <v>824</v>
       </c>
       <c r="H13" t="n">
-        <v>0.32</v>
+        <v>7.58</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>26100</v>
+        <v>250500</v>
       </c>
       <c r="K13" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>323617520750</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>20000</v>
+        <v>-415000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락 및 변동성에 대한 심리적 불안감 속에서 일부 긍정적인 신호 포착. 외인 수급 변화에 대한 관심.</t>
+          <t>반도체 수출 데이터 호조 및 공매도 청산 요구가 있으나, 주가 하락에 대한 우려도 존재함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['변동성', '외인 수급', '심리']</t>
+          <t>['반도체 수출', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52200</v>
+        <v>1904</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.44</v>
+        <v>0.32</v>
       </c>
       <c r="E14" t="n">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G14" t="n">
-        <v>158</v>
+        <v>252</v>
       </c>
       <c r="H14" t="n">
-        <v>2.92</v>
+        <v>2.44</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>51800</v>
+        <v>1901</v>
       </c>
       <c r="K14" t="n">
-        <v>51300</v>
+        <v>2050</v>
       </c>
       <c r="L14" t="n">
-        <v>54500</v>
+        <v>2080</v>
       </c>
       <c r="M14" t="n">
-        <v>51300</v>
+        <v>1900</v>
       </c>
       <c r="N14" t="n">
-        <v>3.36</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>99248447000</v>
+        <v>42919484139</v>
       </c>
       <c r="P14" t="n">
-        <v>87700</v>
+        <v>4795</v>
       </c>
       <c r="Q14" t="n">
-        <v>17210</v>
+        <v>1524</v>
       </c>
       <c r="R14" t="n">
-        <v>128000</v>
+        <v>-389000</v>
       </c>
       <c r="S14" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>홍해 사태 및 유가 급등으로 인한 전쟁 테마주 부각. VLCC 용선료 폭등과 같은 단기 호재로 인한 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['전쟁 테마주', '유가', 'VLCC']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90200</v>
+        <v>415000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>0.2</v>
       </c>
       <c r="E15" t="n">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="F15" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>886</v>
+        <v>281</v>
       </c>
       <c r="H15" t="n">
-        <v>23.59</v>
+        <v>38.02</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>89900</v>
+        <v>415500</v>
       </c>
       <c r="K15" t="n">
-        <v>88700</v>
+        <v>407000</v>
       </c>
       <c r="L15" t="n">
-        <v>91000</v>
+        <v>418000</v>
       </c>
       <c r="M15" t="n">
-        <v>88000</v>
+        <v>404000</v>
       </c>
       <c r="N15" t="n">
-        <v>23.65</v>
+        <v>37.82</v>
       </c>
       <c r="O15" t="n">
-        <v>162087319100</v>
+        <v>59167856000</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>822000</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>283000</v>
       </c>
       <c r="R15" t="n">
-        <v>-289000</v>
+        <v>23000</v>
       </c>
       <c r="S15" t="n">
-        <v>70000</v>
+        <v>5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 에너지 투자 협상 타결 및 원전 사업 수주 기대감 부각. 대규모 수주 잔고와 연기금 매수세에 따른 상승 전망.</t>
+          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['에너지 협상', '원전 수주', '수주 잔고']</t>
+          <t>['수주', '로봇', '미래차']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19725</v>
+        <v>50400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="F16" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>524</v>
+        <v>612</v>
       </c>
       <c r="H16" t="n">
-        <v>10.65</v>
+        <v>38.78</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19750</v>
+        <v>50800</v>
       </c>
       <c r="K16" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>19960</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>19060</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>10.64</v>
+        <v>38.69</v>
       </c>
       <c r="O16" t="n">
-        <v>110480590660</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-76000</v>
+        <v>-163000</v>
       </c>
       <c r="S16" t="n">
-        <v>-15000</v>
+        <v>31000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차 해지 운동 독려 및 공매도 세력과의 전쟁 선포. 원전 8기 대미 투자 관련 뉴스 언급. 목표가 상향 소식과 함께 2만원 이상 주가 상승 기대.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시가 확인되었으며, 이에 따른 주가 상승 기대감이 높음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '원전']</t>
+          <t>['수주', '공시']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>414500</v>
+        <v>29550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>276</v>
+        <v>157</v>
       </c>
       <c r="H17" t="n">
-        <v>38.02</v>
+        <v>25.55</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>415500</v>
+        <v>29800</v>
       </c>
       <c r="K17" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>418000</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>37.82</v>
+        <v>24.99</v>
       </c>
       <c r="O17" t="n">
-        <v>57928050500</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['수주', '로봇', '미래차']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50400</v>
+        <v>8860</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>603</v>
+        <v>285</v>
       </c>
       <c r="H18" t="n">
-        <v>38.78</v>
+        <v>27.19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>50800</v>
+        <v>8950</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>38.69</v>
+        <v>27.16</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>17984000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2091,23 +2091,23 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-163000</v>
+        <v>-34000</v>
       </c>
       <c r="S18" t="n">
-        <v>31000</v>
+        <v>-198000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['수주', '공시', '대규모']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,43 +2115,43 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8840</v>
+        <v>89900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>233</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="G19" t="n">
-        <v>280</v>
+        <v>899</v>
       </c>
       <c r="H19" t="n">
-        <v>27.19</v>
+        <v>23.59</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8970</v>
+        <v>91700</v>
       </c>
       <c r="K19" t="n">
-        <v>8780</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>8880</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>8680</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>27.16</v>
+        <v>23.65</v>
       </c>
       <c r="O19" t="n">
-        <v>17625397170</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-289000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
+          <t>미국 에너지 투자 협상 타결 및 원전 사업 수주 기대감 부각. 대규모 수주 잔고와 연기금 매수세에 따른 상승 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['경영부진', '주가하락', '디스플레이']</t>
+          <t>['에너지 협상', '원전 수주', '수주 잔고']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2223,21 +2223,21 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7860</v>
+        <v>7790</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-2.50%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
         <v>128</v>
@@ -2266,7 +2266,7 @@
         <v>0.46</v>
       </c>
       <c r="O20" t="n">
-        <v>85846000000</v>
+        <v>86566000000</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2311,162 +2311,162 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3555</v>
+        <v>1799000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-2.91%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>434</v>
       </c>
       <c r="G21" t="n">
-        <v>156</v>
+        <v>1921</v>
       </c>
       <c r="H21" t="n">
-        <v>0.73</v>
+        <v>50.55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>3620</v>
+        <v>1853000</v>
       </c>
       <c r="K21" t="n">
-        <v>3725</v>
+        <v>1773000</v>
       </c>
       <c r="L21" t="n">
-        <v>3915</v>
+        <v>1812000</v>
       </c>
       <c r="M21" t="n">
-        <v>3520</v>
+        <v>1768000</v>
       </c>
       <c r="N21" t="n">
-        <v>1.54</v>
+        <v>50.67</v>
       </c>
       <c r="O21" t="n">
-        <v>47058777486</v>
+        <v>3570676750000</v>
       </c>
       <c r="P21" t="n">
-        <v>4335</v>
+        <v>2987000</v>
       </c>
       <c r="Q21" t="n">
-        <v>1246</v>
+        <v>305500</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>-402000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-168000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>기관 매수세 유입 및 일부 호재 언급이 있으나, CPI 발표 등 불확실성 요인도 존재함.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['기관 매수', 'CPI']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14050</v>
+        <v>259250</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>-3.62%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>109</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>60</v>
+        <v>502</v>
       </c>
       <c r="G22" t="n">
-        <v>641</v>
+        <v>1801</v>
       </c>
       <c r="H22" t="n">
-        <v>5.98</v>
+        <v>46.71</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>14320</v>
+        <v>269000</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>256500</v>
       </c>
       <c r="N22" t="n">
-        <v>6.09</v>
+        <v>46.81</v>
       </c>
       <c r="O22" t="n">
-        <v>104494000000</v>
+        <v>2712887723000</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R22" t="n">
-        <v>-290000</v>
+        <v>-2974000</v>
       </c>
       <c r="S22" t="n">
-        <v>-96000</v>
+        <v>-1056000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>자포리 원전 이슈 및 미국 원전 섹터 강세에 따른 기대감 형성. 모건스텐리 대규모 매수세 유입 및 120일선 지지선 중요성 강조. 원전 섹터 주도주 역할 기대.</t>
+          <t>정치적 이슈와 관련된 부정적 언급이 다수이며, 주가 관련 근거 있는 분석은 부재함.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,90 +2475,90 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전', '자포리', '모건스텐리']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>193000</v>
+        <v>14050</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.28%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E23" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>151</v>
+        <v>663</v>
       </c>
       <c r="H23" t="n">
-        <v>75.98999999999999</v>
+        <v>5.98</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>197500</v>
+        <v>14600</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>14950</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>14020</v>
       </c>
       <c r="N23" t="n">
-        <v>75.92</v>
+        <v>6.09</v>
       </c>
       <c r="O23" t="n">
-        <v>465319000000</v>
+        <v>105859618530</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3540</v>
       </c>
       <c r="R23" t="n">
-        <v>-1070000</v>
+        <v>-290000</v>
       </c>
       <c r="S23" t="n">
-        <v>-84000</v>
+        <v>-96000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>자포리 원전 이슈 및 미국 원전 섹터 강세에 따른 기대감 형성. 모건스텐리 대규모 매수세 유입 및 120일선 지지선 중요성 강조. 원전 섹터 주도주 역할 기대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['원전', '자포리', '모건스텐리']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28700</v>
+        <v>15040</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G24" t="n">
-        <v>154</v>
+        <v>295</v>
       </c>
       <c r="H24" t="n">
-        <v>51.4</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,38 +2619,38 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>29550</v>
+        <v>15640</v>
       </c>
       <c r="K24" t="n">
-        <v>28650</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>28900</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>28500</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>24.99</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>48484473825</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>410000</v>
+        <v>16000</v>
       </c>
       <c r="S24" t="n">
-        <v>-200000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,38 +2672,38 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1793000</v>
+        <v>7380</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>-3.91%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>800</v>
+        <v>132</v>
       </c>
       <c r="F25" t="n">
-        <v>445</v>
+        <v>62</v>
       </c>
       <c r="G25" t="n">
-        <v>1885</v>
+        <v>473</v>
       </c>
       <c r="H25" t="n">
-        <v>50.55</v>
+        <v>11.72</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,51 +2711,51 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1856000</v>
+        <v>7680</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>7660</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>7340</v>
       </c>
       <c r="N25" t="n">
-        <v>50.67</v>
+        <v>11.62</v>
       </c>
       <c r="O25" t="n">
-        <v>3481233000000</v>
+        <v>10825545905</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>8850</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4220</v>
       </c>
       <c r="R25" t="n">
-        <v>-402000</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-168000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>중동 평화 회담 및 금리 하락 가능성에 따른 반등 기대감. 개인 투자자 매수세 유입 및 CPI 발표 주시.</t>
+          <t>주가 상승을 저해하는 요인들이 언급되며, 주가에 대한 불확실성이 존재함.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '금리', 'CPI']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,38 +2764,38 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15040</v>
+        <v>192900</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G26" t="n">
-        <v>289</v>
+        <v>151</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,38 +2803,38 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>15640</v>
+        <v>203000</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>195600</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>191000</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>75.92</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>474452096250</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>243500</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>58600</v>
       </c>
       <c r="R26" t="n">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,130 +2856,130 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>258250</v>
+        <v>14180</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-4.00%</t>
+          <t>-5.21%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="E27" t="n">
-        <v>800</v>
+        <v>119</v>
       </c>
       <c r="F27" t="n">
-        <v>504</v>
+        <v>62</v>
       </c>
       <c r="G27" t="n">
-        <v>1819</v>
+        <v>330</v>
       </c>
       <c r="H27" t="n">
-        <v>46.71</v>
+        <v>2.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>269000</v>
+        <v>14960</v>
       </c>
       <c r="K27" t="n">
-        <v>258000</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>256500</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>46.81</v>
+        <v>2.89</v>
       </c>
       <c r="O27" t="n">
-        <v>2647712961250</v>
+        <v>60663000000</v>
       </c>
       <c r="P27" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>72100</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-2974000</v>
+        <v>-282000</v>
       </c>
       <c r="S27" t="n">
-        <v>-1056000</v>
+        <v>-19000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 증권 정보 시스템 불편함에 대한 불만 표출. 반도체 섹터 전반의 약세와 삼성전자 주가 부진에 대한 언급.</t>
+          <t>광통신 대장주로서의 지위 재확인 및 외국인 매수세 유입 언급. 오후 흐름 및 월요일 강한 상승 기대감 형성. 2만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['정치 이슈', '반도체', '증권 정보']</t>
+          <t>['광통신', '외국인 매수', '대장주']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12120</v>
+        <v>9280</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-4.04%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="F28" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G28" t="n">
-        <v>111</v>
+        <v>334</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2987,38 +2987,38 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>12630</v>
+        <v>9800</v>
       </c>
       <c r="K28" t="n">
-        <v>12520</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>12930</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>12010</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.14</v>
+        <v>4.42</v>
       </c>
       <c r="O28" t="n">
-        <v>63384877915</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>20850</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-106000</v>
+        <v>-97000</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '거래량']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3040,38 +3040,38 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14180</v>
+        <v>12120</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-5.21%</t>
+          <t>-6.98%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.39</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="F29" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G29" t="n">
-        <v>320</v>
+        <v>112</v>
       </c>
       <c r="H29" t="n">
-        <v>2.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>14960</v>
+        <v>13030</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.89</v>
+        <v>0.14</v>
       </c>
       <c r="O29" t="n">
-        <v>59965000000</v>
+        <v>63604000000</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -3103,14 +3103,14 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>-282000</v>
+        <v>-106000</v>
       </c>
       <c r="S29" t="n">
-        <v>-19000</v>
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>광통신 대장주로서의 지위 재확인 및 외국인 매수세 유입 언급. 오후 흐름 및 월요일 강한 상승 기대감 형성. 2만원 목표가 제시.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
@@ -3119,11 +3119,11 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수', '대장주']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3132,38 +3132,38 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9280</v>
+        <v>3560</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-7.89%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F30" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G30" t="n">
-        <v>334</v>
+        <v>160</v>
       </c>
       <c r="H30" t="n">
-        <v>4.49</v>
+        <v>0.73</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>9800</v>
+        <v>3865</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3183,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.42</v>
+        <v>1.54</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>47229000000</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -3195,14 +3195,14 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>-97000</v>
+        <v>-36000</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -3211,11 +3211,11 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3224,90 +3224,90 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>232500</v>
+        <v>26400</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-8.10%</t>
+          <t>-12.87%</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.96</v>
+        <v>-0.01</v>
       </c>
       <c r="E31" t="n">
-        <v>233</v>
+        <v>311</v>
       </c>
       <c r="F31" t="n">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G31" t="n">
-        <v>806</v>
+        <v>506</v>
       </c>
       <c r="H31" t="n">
-        <v>7.58</v>
+        <v>0.32</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>253000</v>
+        <v>30300</v>
       </c>
       <c r="K31" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>8.539999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="O31" t="n">
-        <v>203024376000</v>
+        <v>324382000000</v>
       </c>
       <c r="P31" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>-415000</v>
+        <v>20000</v>
       </c>
       <c r="S31" t="n">
-        <v>-42000</v>
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 강한 비판 및 청산 요구. 반도체 수출 호조 뉴스에도 불구하고 주가 하락에 대한 불만 표출.</t>
+          <t>주가 하락에 대한 부정적 심리가 강하며, 명확한 사실 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>['공매도', '반도체 수출', '주가 하락']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>386380</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_14.xlsx
+++ b/data/trending_integrated_20260911_14.xlsx
@@ -581,10 +581,10 @@
         <v>141</v>
       </c>
       <c r="F2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>208118000000</v>
+        <v>208151000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 다음 핵심 시장으로 사이버 보안 부문 지목. 젠슨 황 발언에 따른 보안 섹터 급등 및 엑스게이트 수혜 전망. 594억 공급계약 및 모건스텐리 매집 호재.</t>
+          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 지목과 함께, 양자 보안 기술 상용화 및 공급 계약 소식이 부각되며 강한 상승세를 보임.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버 보안', '젠슨 황', '공급계약']</t>
+          <t>['사이버 보안', '양자 보안', '젠슨 황']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>비엘팜텍</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2720</v>
+        <v>2695</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+25.93%</t>
+          <t>+26.82%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>355</v>
+        <v>192</v>
       </c>
       <c r="H3" t="n">
-        <v>1.32</v>
+        <v>3.83</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2160</v>
+        <v>2125</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2725</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N3" t="n">
-        <v>1.36</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>8080000000</v>
+        <v>113989728393</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R3" t="n">
-        <v>220000</v>
+        <v>-1952000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
+          <t>미국 정부의 양자컴퓨터 보조금 지원 체결 소식이 호재로 작용하며, 높은 거래량 대비 주가 상승 탄력에 대한 논의가 있음.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
+          <t>['양자컴퓨터', '보조금', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,82 +735,82 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>065170</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2630</v>
+        <v>16180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+23.76%</t>
+          <t>+21.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="E4" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H4" t="n">
-        <v>3.83</v>
+        <v>1.24</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2125</v>
+        <v>13340</v>
       </c>
       <c r="K4" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2692</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
-        <v>107962739110</v>
+        <v>160505000000</v>
       </c>
       <c r="P4" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-2091000</v>
+        <v>6000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>594억 공급 계약 및 모건스탠리 48만주 매집 공시 확인. 미국 정부 양자컴퓨터 보조금 지원 관련 기대감. 거래량 증가와 함께 손바뀜 가능성 제기.</t>
+          <t>K-뷰티 대장주로서의 기대감과 함께 급등세 지속 전망. 경영권 이슈 및 전고점 돌파 기대감 반영. 알바 언급 및 매수세 유입 추측.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공급계약', '양자컴퓨터', '매집공시']</t>
+          <t>['K-뷰티', '대장주', '경영권']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14960</v>
+        <v>135500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+23.74%</t>
+          <t>+17.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.11</v>
+        <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>448</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
-        <v>253</v>
+        <v>111</v>
       </c>
       <c r="G5" t="n">
-        <v>958</v>
+        <v>331</v>
       </c>
       <c r="H5" t="n">
-        <v>3.14</v>
+        <v>4.32</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12090</v>
+        <v>115700</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03</v>
+        <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>205865000000</v>
+        <v>487565980250</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R5" t="n">
-        <v>-386000</v>
+        <v>39000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>119000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
+          <t>폭발적인 거래량 동반 상승세에 대한 기대감이 있으나, 급격한 상승 후 매물 소화 및 추가 상승 여부에 대한 관망세가 나타남.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁 테마', 'WTI']</t>
+          <t>['거래량', '상승', '매물 소화']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,46 +924,46 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16450</v>
+        <v>7300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+23.31%</t>
+          <t>+11.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.19</v>
+        <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="G6" t="n">
-        <v>165</v>
+        <v>373</v>
       </c>
       <c r="H6" t="n">
-        <v>1.24</v>
+        <v>2.15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13340</v>
+        <v>6570</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.43</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>154108000000</v>
+        <v>166145000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -987,67 +987,67 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>36000</v>
+        <v>170000</v>
       </c>
       <c r="S6" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>K-뷰티 대장주로서의 기대감과 함께 급등세 지속 전망. 경영권 이슈 및 전고점 돌파 기대감 반영. 알바 언급 및 매수세 유입 추측.</t>
+          <t>광통신 및 위성 네트워크 관련 섹터에서 대장주로 언급되며, 주가 상승에 대한 기대감과 함께 힘이 없다는 의견도 공존함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['K-뷰티', '대장주', '경영권']</t>
+          <t>['광통신', '위성네트워크', '대장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>136100</v>
+        <v>7680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+17.02%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.26</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="F7" t="n">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>327</v>
+        <v>476</v>
       </c>
       <c r="H7" t="n">
-        <v>4.32</v>
+        <v>11.72</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>116300</v>
+        <v>7100</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.58</v>
+        <v>11.62</v>
       </c>
       <c r="O7" t="n">
-        <v>483812000000</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1079,14 +1079,14 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>39000</v>
+        <v>45000</v>
       </c>
       <c r="S7" t="n">
-        <v>95000</v>
+        <v>1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>매출 호조 및 상승 기대감이 있으나, 구체적인 거래량이나 상승 이유에 대한 명확한 분석은 부족함.</t>
+          <t>뉴스 기반 주가 상승 기대와 함께 개인 투자자의 자금 이탈 및 기관 매수 가능성에 대한 언급이 혼재되어 있음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['거래량', '상승']</t>
+          <t>['주가 상승', '기관 매수', '개인 투자자']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7340</v>
+        <v>15050</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+11.72%</t>
+          <t>+3.72%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.79</v>
+        <v>3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>121</v>
+        <v>453</v>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="G8" t="n">
-        <v>365</v>
+        <v>988</v>
       </c>
       <c r="H8" t="n">
-        <v>2.15</v>
+        <v>3.14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6570</v>
+        <v>14510</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>17010</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>17310</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>14840</v>
       </c>
       <c r="N8" t="n">
-        <v>2.94</v>
+        <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>165038000000</v>
+        <v>206778261490</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>36200</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>8920</v>
       </c>
       <c r="R8" t="n">
-        <v>110000</v>
+        <v>-339000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>광통신 및 위성네트워크 섹터의 대장주로 부각되며 상승 기대감 형성. 보안 관련 이슈 및 공매도 세력 약화 분석. 급등 가능성 및 월요일 전망.</t>
+          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '보안']</t>
+          <t>['국제유가', '전쟁 테마', 'WTI']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7740</v>
+        <v>26950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.31%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>244</v>
+        <v>320</v>
       </c>
       <c r="F9" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="G9" t="n">
-        <v>1136</v>
+        <v>515</v>
       </c>
       <c r="H9" t="n">
-        <v>1.29</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7420</v>
+        <v>26100</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>26350</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>25400</v>
       </c>
       <c r="N9" t="n">
-        <v>1.17</v>
+        <v>0.33</v>
       </c>
       <c r="O9" t="n">
-        <v>29479000000</v>
+        <v>328126470100</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R9" t="n">
-        <v>-73000</v>
+        <v>2000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>세계폐암학회(WCLC) 데이터 발표를 통한 주가 대폭등이 예고되었으며, 임상 시험 디자인이 언급됨.</t>
+          <t>주가 하락에 대한 부정적 심리가 강하며, 명확한 사실 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['임상 시험', 'WCLC']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3920</v>
+        <v>3910</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.89%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
         <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H10" t="n">
         <v>1.04</v>
@@ -1346,7 +1346,7 @@
         <v>1.57</v>
       </c>
       <c r="O10" t="n">
-        <v>93475000000</v>
+        <v>93925000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-582000</v>
+        <v>-560000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1391,92 +1391,92 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19730</v>
+        <v>7810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="F11" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>542</v>
+        <v>128</v>
       </c>
       <c r="H11" t="n">
-        <v>10.65</v>
+        <v>0.52</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19450</v>
+        <v>7690</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>7670</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>9170</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>7450</v>
       </c>
       <c r="N11" t="n">
-        <v>10.64</v>
+        <v>0.46</v>
       </c>
       <c r="O11" t="n">
-        <v>113121000000</v>
+        <v>87301253820</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>9170</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="R11" t="n">
-        <v>-76000</v>
+        <v>14000</v>
       </c>
       <c r="S11" t="n">
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대차해지 관련 주주 독려와 목표가 상향 뉴스가 언급되었으나, 구체적인 근거는 부족함.</t>
+          <t>포스코 지정 가공센터로서 공급 계약 체결 및 실적 기대감 형성. 유통물량 부족에 따른 급등 가능성 언급. 단기 급락 및 변동성 경계 신호.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차해지', '목표가']</t>
+          <t>['공급 계약', '포스코', '품절주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1498,13 @@
         <v>-0.44</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
         <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H12" t="n">
         <v>2.92</v>
@@ -1530,7 +1530,7 @@
         <v>3.36</v>
       </c>
       <c r="O12" t="n">
-        <v>100140770400</v>
+        <v>101192415000</v>
       </c>
       <c r="P12" t="n">
         <v>87700</v>
@@ -1539,10 +1539,10 @@
         <v>17210</v>
       </c>
       <c r="R12" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="S12" t="n">
-        <v>24000</v>
+        <v>34000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         <v>-0.96</v>
       </c>
       <c r="E13" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G13" t="n">
-        <v>824</v>
+        <v>837</v>
       </c>
       <c r="H13" t="n">
         <v>7.58</v>
@@ -1631,14 +1631,14 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-415000</v>
+        <v>-484000</v>
       </c>
       <c r="S13" t="n">
-        <v>-42000</v>
+        <v>-43000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 수출 데이터 호조 및 공매도 청산 요구가 있으나, 주가 하락에 대한 우려도 존재함.</t>
+          <t>공매도 세력과의 공방이 치열한 가운데, 주가 하락에 대한 우려와 함께 매수 후 소각 등 주주 가치 제고 방안에 대한 요구가 나타나고 있음.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체 수출', '공매도']</t>
+          <t>['공매도', '주가 하락', '매수 소각']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1904</v>
+        <v>50800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="F14" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="G14" t="n">
-        <v>252</v>
+        <v>622</v>
       </c>
       <c r="H14" t="n">
-        <v>2.44</v>
+        <v>38.78</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1901</v>
+        <v>50400</v>
       </c>
       <c r="K14" t="n">
-        <v>2050</v>
+        <v>50500</v>
       </c>
       <c r="L14" t="n">
-        <v>2080</v>
+        <v>51200</v>
       </c>
       <c r="M14" t="n">
-        <v>1900</v>
+        <v>49650</v>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>38.69</v>
       </c>
       <c r="O14" t="n">
-        <v>42919484139</v>
+        <v>71916151775</v>
       </c>
       <c r="P14" t="n">
-        <v>4795</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>1524</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>-389000</v>
+        <v>-170000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 급등으로 인한 전쟁 테마주 부각. VLCC 용선료 폭등과 같은 단기 호재로 인한 상승 기대감 형성.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시가 확인되었으며, 이에 따른 주가 상승 기대감이 높음.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '유가', 'VLCC']</t>
+          <t>['수주', '공시']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>415000</v>
+        <v>90400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="G15" t="n">
-        <v>281</v>
+        <v>912</v>
       </c>
       <c r="H15" t="n">
-        <v>38.02</v>
+        <v>23.59</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>415500</v>
+        <v>89900</v>
       </c>
       <c r="K15" t="n">
-        <v>407000</v>
+        <v>88700</v>
       </c>
       <c r="L15" t="n">
-        <v>418000</v>
+        <v>91000</v>
       </c>
       <c r="M15" t="n">
-        <v>404000</v>
+        <v>88000</v>
       </c>
       <c r="N15" t="n">
-        <v>37.82</v>
+        <v>23.65</v>
       </c>
       <c r="O15" t="n">
-        <v>59167856000</v>
+        <v>168910061100</v>
       </c>
       <c r="P15" t="n">
-        <v>822000</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>283000</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>23000</v>
+        <v>-309000</v>
       </c>
       <c r="S15" t="n">
-        <v>5000</v>
+        <v>77000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
+          <t>미국 에너지 투자 협상 타결 및 원전 사업 수주 기대감 부각. 대규모 수주 잔고와 연기금 매수세에 따른 상승 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '로봇', '미래차']</t>
+          <t>['에너지 협상', '원전 수주', '수주 잔고']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50400</v>
+        <v>19800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G16" t="n">
-        <v>612</v>
+        <v>550</v>
       </c>
       <c r="H16" t="n">
-        <v>38.78</v>
+        <v>10.65</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>50800</v>
+        <v>19750</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>19960</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>19060</v>
       </c>
       <c r="N16" t="n">
-        <v>38.69</v>
+        <v>10.64</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>115236038310</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-163000</v>
+        <v>28000</v>
       </c>
       <c r="S16" t="n">
-        <v>31000</v>
+        <v>-44000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대형 수주 공시가 확인되었으며, 이에 따른 주가 상승 기대감이 높음.</t>
+          <t>대차해지 관련 주주 독려와 목표가 상향 뉴스가 언급되었으나, 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['수주', '공시']</t>
+          <t>['대차해지', '목표가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29550</v>
+        <v>1903</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="H17" t="n">
-        <v>25.55</v>
+        <v>2.44</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29800</v>
+        <v>1901</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="N17" t="n">
-        <v>24.99</v>
+        <v>2.12</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>43180854445</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4795</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-445000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>홍해 사태 및 유가 급등 관련 전쟁 테마주로 분류되며, VLCC 용선료 폭등 소식이 전해지고 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['전쟁 테마주', 'VLCC', '유가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8860</v>
+        <v>415000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H18" t="n">
-        <v>27.19</v>
+        <v>38.02</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8950</v>
+        <v>415500</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N18" t="n">
-        <v>27.16</v>
+        <v>37.82</v>
       </c>
       <c r="O18" t="n">
-        <v>17984000000</v>
+        <v>60755818250</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R18" t="n">
-        <v>-34000</v>
+        <v>30000</v>
       </c>
       <c r="S18" t="n">
-        <v>-198000</v>
+        <v>5000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
+          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['경영부진', '주가하락', '디스플레이']</t>
+          <t>['수주', '로봇', '미래차']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>89900</v>
+        <v>8870</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E19" t="n">
-        <v>233</v>
+        <v>96</v>
       </c>
       <c r="F19" t="n">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>899</v>
+        <v>286</v>
       </c>
       <c r="H19" t="n">
-        <v>23.59</v>
+        <v>27.19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,91 +2159,91 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>91700</v>
+        <v>8970</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>8780</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>8890</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>8680</v>
       </c>
       <c r="N19" t="n">
-        <v>23.65</v>
+        <v>27.16</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>18354578440</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>-289000</v>
+        <v>-9000</v>
       </c>
       <c r="S19" t="n">
-        <v>70000</v>
+        <v>-243000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 에너지 투자 협상 타결 및 원전 사업 수주 기대감 부각. 대규모 수주 잔고와 연기금 매수세에 따른 상승 전망.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['에너지 협상', '원전 수주', '수주 잔고']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7790</v>
+        <v>14040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.50%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>128</v>
+        <v>669</v>
       </c>
       <c r="H20" t="n">
-        <v>0.52</v>
+        <v>5.98</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7990</v>
+        <v>14320</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2263,10 +2263,10 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.46</v>
+        <v>6.09</v>
       </c>
       <c r="O20" t="n">
-        <v>86566000000</v>
+        <v>106864000000</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2275,14 +2275,14 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>포스코 지정 가공센터로서 공급 계약 체결 및 실적 기대감 형성. 유통물량 부족에 따른 급등 가능성 언급. 단기 급락 및 변동성 경계 신호.</t>
+          <t>자포리 원전 이슈 및 미국 원전 섹터 강세에 따른 기대감 형성. 모건스텐리 대규모 매수세 유입 및 120일선 지지선 중요성 강조. 원전 섹터 주도주 역할 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공급 계약', '포스코', '품절주']</t>
+          <t>['원전', '자포리', '모건스텐리']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1799000</v>
+        <v>14710</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.91%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>86</v>
       </c>
       <c r="F21" t="n">
-        <v>434</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>1921</v>
+        <v>296</v>
       </c>
       <c r="H21" t="n">
-        <v>50.55</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,91 +2343,91 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1853000</v>
+        <v>15040</v>
       </c>
       <c r="K21" t="n">
-        <v>1773000</v>
+        <v>14550</v>
       </c>
       <c r="L21" t="n">
-        <v>1812000</v>
+        <v>15260</v>
       </c>
       <c r="M21" t="n">
-        <v>1768000</v>
+        <v>14350</v>
       </c>
       <c r="N21" t="n">
-        <v>50.67</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3570676750000</v>
+        <v>21183857475</v>
       </c>
       <c r="P21" t="n">
-        <v>2987000</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>305500</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>-402000</v>
+        <v>23000</v>
       </c>
       <c r="S21" t="n">
-        <v>-168000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>기관 매수세 유입 및 일부 호재 언급이 있으나, CPI 발표 등 불확실성 요인도 존재함.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['기관 매수', 'CPI']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>259250</v>
+        <v>193000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.62%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
-        <v>502</v>
+        <v>59</v>
       </c>
       <c r="G22" t="n">
-        <v>1801</v>
+        <v>152</v>
       </c>
       <c r="H22" t="n">
-        <v>46.71</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>269000</v>
+        <v>197500</v>
       </c>
       <c r="K22" t="n">
-        <v>258000</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>256500</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>46.81</v>
+        <v>75.92</v>
       </c>
       <c r="O22" t="n">
-        <v>2712887723000</v>
+        <v>483725000000</v>
       </c>
       <c r="P22" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>72100</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-2974000</v>
+        <v>-1185000</v>
       </c>
       <c r="S22" t="n">
-        <v>-1056000</v>
+        <v>-57000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급이 다수이며, 주가 관련 근거 있는 분석은 부재함.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,90 +2475,90 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14050</v>
+        <v>28700</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G23" t="n">
-        <v>663</v>
+        <v>163</v>
       </c>
       <c r="H23" t="n">
-        <v>5.98</v>
+        <v>51.43</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14600</v>
+        <v>29550</v>
       </c>
       <c r="K23" t="n">
-        <v>14800</v>
+        <v>28650</v>
       </c>
       <c r="L23" t="n">
-        <v>14950</v>
+        <v>28900</v>
       </c>
       <c r="M23" t="n">
-        <v>14020</v>
+        <v>28500</v>
       </c>
       <c r="N23" t="n">
-        <v>6.09</v>
+        <v>24.99</v>
       </c>
       <c r="O23" t="n">
-        <v>105859618530</v>
+        <v>50999976300</v>
       </c>
       <c r="P23" t="n">
-        <v>30200</v>
+        <v>31200</v>
       </c>
       <c r="Q23" t="n">
-        <v>3540</v>
+        <v>21000</v>
       </c>
       <c r="R23" t="n">
-        <v>-290000</v>
+        <v>594000</v>
       </c>
       <c r="S23" t="n">
-        <v>-96000</v>
+        <v>-269000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>자포리 원전 이슈 및 미국 원전 섹터 강세에 따른 기대감 형성. 모건스텐리 대규모 매수세 유입 및 120일선 지지선 중요성 강조. 원전 섹터 주도주 역할 기대.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['원전', '자포리', '모건스텐리']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,46 +2580,46 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15040</v>
+        <v>2095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E24" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>295</v>
+        <v>368</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>15640</v>
+        <v>2160</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2643,14 +2643,14 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>16000</v>
+        <v>219000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
+          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
+          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,38 +2672,38 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>065170</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7380</v>
+        <v>1795500</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-3.10%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="E25" t="n">
-        <v>132</v>
+        <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>62</v>
+        <v>439</v>
       </c>
       <c r="G25" t="n">
-        <v>473</v>
+        <v>1967</v>
       </c>
       <c r="H25" t="n">
-        <v>11.72</v>
+        <v>50.55</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,51 +2711,51 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>7680</v>
+        <v>1853000</v>
       </c>
       <c r="K25" t="n">
-        <v>7540</v>
+        <v>1773000</v>
       </c>
       <c r="L25" t="n">
-        <v>7660</v>
+        <v>1812000</v>
       </c>
       <c r="M25" t="n">
-        <v>7340</v>
+        <v>1768000</v>
       </c>
       <c r="N25" t="n">
-        <v>11.62</v>
+        <v>50.67</v>
       </c>
       <c r="O25" t="n">
-        <v>10825545905</v>
+        <v>3652592970000</v>
       </c>
       <c r="P25" t="n">
-        <v>8850</v>
+        <v>2987000</v>
       </c>
       <c r="Q25" t="n">
-        <v>4220</v>
+        <v>305500</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>-389000</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-179000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>주가 상승을 저해하는 요인들이 언급되며, 주가에 대한 불확실성이 존재함.</t>
+          <t>중동 평화 회담 선언 및 유가 하락 등 대외 변수에 영향을 받으며, 기관 매수세 유입에 따른 반등 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['중동', '유가', '기관 매수']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,138 +2764,138 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>192900</v>
+        <v>14170</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-4.98%</t>
+          <t>-3.87%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="E26" t="n">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="F26" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G26" t="n">
-        <v>151</v>
+        <v>428</v>
       </c>
       <c r="H26" t="n">
-        <v>75.98999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>203000</v>
+        <v>14740</v>
       </c>
       <c r="K26" t="n">
-        <v>195000</v>
+        <v>14050</v>
       </c>
       <c r="L26" t="n">
-        <v>195600</v>
+        <v>14560</v>
       </c>
       <c r="M26" t="n">
-        <v>191000</v>
+        <v>14030</v>
       </c>
       <c r="N26" t="n">
-        <v>75.92</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
-        <v>474452096250</v>
+        <v>61245478140</v>
       </c>
       <c r="P26" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q26" t="n">
-        <v>58600</v>
+        <v>1272</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>-303000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-28000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>광통신 섹터 내에서 대장주로 언급되며, 매수 기회를 주는 흐름 속에서 추가 상승에 대한 기대감이 나타나고 있음.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['광통신', '대장주', '매수세']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14180</v>
+        <v>259000</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-5.21%</t>
+          <t>-3.90%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.39</v>
+        <v>-0.1</v>
       </c>
       <c r="E27" t="n">
-        <v>119</v>
+        <v>800</v>
       </c>
       <c r="F27" t="n">
-        <v>62</v>
+        <v>497</v>
       </c>
       <c r="G27" t="n">
-        <v>330</v>
+        <v>1825</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5</v>
+        <v>46.71</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>14960</v>
+        <v>269500</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.89</v>
+        <v>46.81</v>
       </c>
       <c r="O27" t="n">
-        <v>60663000000</v>
+        <v>2760826000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2919,36 +2919,36 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-282000</v>
+        <v>-3107000</v>
       </c>
       <c r="S27" t="n">
-        <v>-19000</v>
+        <v>-1180000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>광통신 대장주로서의 지위 재확인 및 외국인 매수세 유입 언급. 오후 흐름 및 월요일 강한 상승 기대감 형성. 2만원 목표가 제시.</t>
+          <t>정치적 이슈와 맞물려 하락하며, 반도체 섹터 전반의 약세와 함께 개별적인 이슈에 대한 언급이 혼재함.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수', '대장주']</t>
+          <t>['정치적 이슈', '반도체', '하락']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2970,10 +2970,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G28" t="n">
         <v>334</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-97000</v>
+        <v>-88000</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -3047,31 +3047,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12120</v>
+        <v>7700</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>-7.23%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.8</v>
+        <v>0.12</v>
       </c>
       <c r="E29" t="n">
-        <v>104</v>
+        <v>250</v>
       </c>
       <c r="F29" t="n">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="G29" t="n">
-        <v>112</v>
+        <v>1179</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3079,47 +3079,47 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>13030</v>
+        <v>8300</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="N29" t="n">
-        <v>0.14</v>
+        <v>1.17</v>
       </c>
       <c r="O29" t="n">
-        <v>63604000000</v>
+        <v>29755516175</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="R29" t="n">
-        <v>-106000</v>
+        <v>-183000</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
+          <t>9월 14일 세계폐암학회(WCLC)에서의 데이터 발표를 앞두고 주가 급등 예고 및 기대감이 형성되고 있으며, 외국계 증권사 유입 소식이 있음.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '거래량']</t>
+          <t>['임상시험', 'WCLC', '데이터 발표']</t>
         </is>
       </c>
       <c r="X29" t="n">
@@ -3127,43 +3127,43 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3560</v>
+        <v>12070</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-7.89%</t>
+          <t>-7.37%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G30" t="n">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="H30" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3865</v>
+        <v>13030</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3183,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.54</v>
+        <v>0.14</v>
       </c>
       <c r="O30" t="n">
-        <v>47229000000</v>
+        <v>64057000000</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -3195,14 +3195,14 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>-36000</v>
+        <v>-105000</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -3211,11 +3211,11 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3224,38 +3224,38 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26400</v>
+        <v>3570</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-12.87%</t>
+          <t>-7.63%</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.01</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>311</v>
+        <v>69</v>
       </c>
       <c r="F31" t="n">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="G31" t="n">
-        <v>506</v>
+        <v>160</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32</v>
+        <v>0.73</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>30300</v>
+        <v>3865</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3275,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.33</v>
+        <v>1.54</v>
       </c>
       <c r="O31" t="n">
-        <v>324382000000</v>
+        <v>47493000000</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3287,14 +3287,14 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 부정적 심리가 강하며, 명확한 사실 기반 분석은 부족함.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -3303,20 +3303,20 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>067290</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_14.xlsx
+++ b/data/trending_integrated_20260911_14.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+27.36%</t>
+          <t>+29.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>96</v>
       </c>
       <c r="G2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -595,31 +595,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12610</v>
+        <v>12360</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16060</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>208151000000</v>
+        <v>208210837225</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>-71000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2695</v>
+        <v>15090</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+26.82%</t>
+          <t>+24.81%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="E3" t="n">
-        <v>123</v>
+        <v>457</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="G3" t="n">
-        <v>192</v>
+        <v>999</v>
       </c>
       <c r="H3" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2125</v>
+        <v>12090</v>
       </c>
       <c r="K3" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2725</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.76</v>
+        <v>0.03</v>
       </c>
       <c r="O3" t="n">
-        <v>113989728393</v>
+        <v>208057000000</v>
       </c>
       <c r="P3" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-1952000</v>
+        <v>-339000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 정부의 양자컴퓨터 보조금 지원 체결 소식이 호재로 작용하며, 높은 거래량 대비 주가 상승 탄력에 대한 논의가 있음.</t>
+          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보조금', '거래량']</t>
+          <t>['국제유가', '전쟁 테마', 'WTI']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,46 +740,46 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16180</v>
+        <v>2640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.29%</t>
+          <t>+23.65%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="H4" t="n">
-        <v>1.24</v>
+        <v>3.83</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13340</v>
+        <v>2135</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.43</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>160505000000</v>
+        <v>117296000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -803,23 +803,23 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>6000</v>
+        <v>-1952000</v>
       </c>
       <c r="S4" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>K-뷰티 대장주로서의 기대감과 함께 급등세 지속 전망. 경영권 이슈 및 전고점 돌파 기대감 반영. 알바 언급 및 매수세 유입 추측.</t>
+          <t>거래량은 높으나 주가 상승 동력이 부족하다는 의견과 함께, 미국 정부의 양자컴퓨터 보조금 지원 뉴스가 언급됨.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['K-뷰티', '대장주', '경영권']</t>
+          <t>['거래량', '양자컴퓨터', '주가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>135500</v>
+        <v>16190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.11%</t>
+          <t>+21.36%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="F5" t="n">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>331</v>
+        <v>185</v>
       </c>
       <c r="H5" t="n">
-        <v>4.32</v>
+        <v>1.24</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>115700</v>
+        <v>13340</v>
       </c>
       <c r="K5" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.58</v>
+        <v>1.43</v>
       </c>
       <c r="O5" t="n">
-        <v>487565980250</v>
+        <v>164937000000</v>
       </c>
       <c r="P5" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>39000</v>
+        <v>6000</v>
       </c>
       <c r="S5" t="n">
-        <v>119000</v>
+        <v>115000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>폭발적인 거래량 동반 상승세에 대한 기대감이 있으나, 급격한 상승 후 매물 소화 및 추가 상승 여부에 대한 관망세가 나타남.</t>
+          <t>K-뷰티 관련 기대감 속에서 일부 상승 흐름이 있으나, 추격 매수 및 단기 이익 실현에 대한 언급도 공존함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['거래량', '상승', '매물 소화']</t>
+          <t>['K-뷰티', '상승세', '추격매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,46 +924,46 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7300</v>
+        <v>137200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+11.11%</t>
+          <t>+17.97%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.79</v>
+        <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="F6" t="n">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G6" t="n">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="H6" t="n">
-        <v>2.15</v>
+        <v>4.32</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6570</v>
+        <v>116300</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>4.58</v>
       </c>
       <c r="O6" t="n">
-        <v>166145000000</v>
+        <v>493408000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -987,14 +987,14 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>170000</v>
+        <v>39000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광통신 및 위성 네트워크 관련 섹터에서 대장주로 언급되며, 주가 상승에 대한 기대감과 함께 힘이 없다는 의견도 공존함.</t>
+          <t>폭발적인 거래량 동반 상승세에 대한 기대감이 있으나, 급격한 상승 후 매물 소화 및 추가 상승 여부에 대한 관망세가 나타남.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '대장주']</t>
+          <t>['거래량', '상승', '매물 소화']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7680</v>
+        <v>7280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+8.66%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>-0.79</v>
       </c>
       <c r="E7" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>476</v>
+        <v>370</v>
       </c>
       <c r="H7" t="n">
-        <v>11.72</v>
+        <v>2.15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7100</v>
+        <v>6700</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6530</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>8370</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6430</v>
       </c>
       <c r="N7" t="n">
-        <v>11.62</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>168372621110</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R7" t="n">
-        <v>45000</v>
+        <v>170000</v>
       </c>
       <c r="S7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뉴스 기반 주가 상승 기대와 함께 개인 투자자의 자금 이탈 및 기관 매수 가능성에 대한 언급이 혼재되어 있음.</t>
+          <t>광통신 및 위성 네트워크 관련 펀드 편입 소식이 있으며, 대장주로서의 역할과 공매도 감소에 대한 기대감이 공존함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 상승', '기관 매수', '개인 투자자']</t>
+          <t>['광통신', '펀드', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15050</v>
+        <v>7680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3.72%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.11</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>453</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>253</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>988</v>
+        <v>483</v>
       </c>
       <c r="H8" t="n">
-        <v>3.14</v>
+        <v>11.72</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14510</v>
+        <v>7100</v>
       </c>
       <c r="K8" t="n">
-        <v>17010</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>17310</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>14840</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03</v>
+        <v>11.62</v>
       </c>
       <c r="O8" t="n">
-        <v>206778261490</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>36200</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8920</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-339000</v>
+        <v>45000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
+          <t>뉴스 기반 주가 상승 기대와 함께 개인 투자자의 자금 이탈 및 기관 매수 가능성에 대한 언급이 혼재되어 있음.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁 테마', 'WTI']</t>
+          <t>['주가 상승', '기관 매수', '개인 투자자']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26950</v>
+        <v>253000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3.26%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>-0.96</v>
       </c>
       <c r="E9" t="n">
-        <v>320</v>
+        <v>246</v>
       </c>
       <c r="F9" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="G9" t="n">
-        <v>515</v>
+        <v>860</v>
       </c>
       <c r="H9" t="n">
-        <v>0.32</v>
+        <v>7.58</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>26100</v>
+        <v>250500</v>
       </c>
       <c r="K9" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>328126470100</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2000</v>
+        <v>-485000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-43000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 부정적 심리가 강하며, 명확한 사실 기반 분석은 부족함.</t>
+          <t>9월 TC본더 수출 데이터 및 공매도 관련 논의가 활발하며, 주가 하락에 대한 우려와 함께 기관 매수세가 언급됨.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['TC본더', '공매도', '기관']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,178 +1292,178 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3910</v>
+        <v>50700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.53</v>
+        <v>0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="G10" t="n">
-        <v>207</v>
+        <v>627</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>38.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3810</v>
+        <v>50400</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>50500</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>51200</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>49650</v>
       </c>
       <c r="N10" t="n">
-        <v>1.57</v>
+        <v>38.69</v>
       </c>
       <c r="O10" t="n">
-        <v>93925000000</v>
+        <v>73128452875</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>-560000</v>
+        <v>-172000</v>
       </c>
       <c r="S10" t="n">
-        <v>14000</v>
+        <v>64000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시가 확인되었으며, 이에 따른 주가 상승 기대감이 높음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['6G통신', '광통신', '데이터센터']</t>
+          <t>['수주', '공시']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7810</v>
+        <v>1903</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.56%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="E11" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>128</v>
+        <v>259</v>
       </c>
       <c r="H11" t="n">
-        <v>0.52</v>
+        <v>2.44</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7690</v>
+        <v>1901</v>
       </c>
       <c r="K11" t="n">
-        <v>7670</v>
+        <v>2050</v>
       </c>
       <c r="L11" t="n">
-        <v>9170</v>
+        <v>2080</v>
       </c>
       <c r="M11" t="n">
-        <v>7450</v>
+        <v>1900</v>
       </c>
       <c r="N11" t="n">
-        <v>0.46</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>87301253820</v>
+        <v>43346852950</v>
       </c>
       <c r="P11" t="n">
-        <v>9170</v>
+        <v>4795</v>
       </c>
       <c r="Q11" t="n">
-        <v>3720</v>
+        <v>1524</v>
       </c>
       <c r="R11" t="n">
-        <v>14000</v>
+        <v>-445000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>포스코 지정 가공센터로서 공급 계약 체결 및 실적 기대감 형성. 유통물량 부족에 따른 급등 가능성 언급. 단기 급락 및 변동성 경계 신호.</t>
+          <t>홍해 사태 및 유가 급등 관련 전쟁 테마주로 분류되며, VLCC 용선료 폭등 소식이 전해지고 있음.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공급 계약', '포스코', '품절주']</t>
+          <t>['전쟁 테마주', 'VLCC', '유가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52400</v>
+        <v>19770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.44</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
-        <v>165</v>
+        <v>557</v>
       </c>
       <c r="H12" t="n">
-        <v>2.92</v>
+        <v>10.65</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>51800</v>
+        <v>19750</v>
       </c>
       <c r="K12" t="n">
-        <v>51300</v>
+        <v>19500</v>
       </c>
       <c r="L12" t="n">
-        <v>54500</v>
+        <v>19960</v>
       </c>
       <c r="M12" t="n">
-        <v>51300</v>
+        <v>19060</v>
       </c>
       <c r="N12" t="n">
-        <v>3.36</v>
+        <v>10.64</v>
       </c>
       <c r="O12" t="n">
-        <v>101192415000</v>
+        <v>117515780985</v>
       </c>
       <c r="P12" t="n">
-        <v>87700</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>127000</v>
+        <v>28000</v>
       </c>
       <c r="S12" t="n">
-        <v>34000</v>
+        <v>-43000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>대차해지 요청과 함께 공매도 관련 논의가 활발하며, 목표가 상향 및 원전 투자 관련 뉴스가 언급됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['대차해지', '공매도', '원전']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253000</v>
+        <v>415500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.96</v>
+        <v>0.2</v>
       </c>
       <c r="E13" t="n">
-        <v>241</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>837</v>
+        <v>289</v>
       </c>
       <c r="H13" t="n">
-        <v>7.58</v>
+        <v>38.02</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>250500</v>
+        <v>415500</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N13" t="n">
-        <v>8.539999999999999</v>
+        <v>37.82</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>62130264750</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R13" t="n">
-        <v>-484000</v>
+        <v>31000</v>
       </c>
       <c r="S13" t="n">
-        <v>-43000</v>
+        <v>5000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 세력과의 공방이 치열한 가운데, 주가 하락에 대한 우려와 함께 매수 후 소각 등 주주 가치 제고 방안에 대한 요구가 나타나고 있음.</t>
+          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '매수 소각']</t>
+          <t>['수주', '로봇', '미래차']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,135 +1655,135 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50800</v>
+        <v>3905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.09</v>
+        <v>-0.53</v>
       </c>
       <c r="E14" t="n">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>622</v>
+        <v>209</v>
       </c>
       <c r="H14" t="n">
-        <v>38.78</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>50400</v>
+        <v>3925</v>
       </c>
       <c r="K14" t="n">
-        <v>50500</v>
+        <v>3810</v>
       </c>
       <c r="L14" t="n">
-        <v>51200</v>
+        <v>4180</v>
       </c>
       <c r="M14" t="n">
-        <v>49650</v>
+        <v>3760</v>
       </c>
       <c r="N14" t="n">
-        <v>38.69</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>71916151775</v>
+        <v>94443945730</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>8100</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>592</v>
       </c>
       <c r="R14" t="n">
-        <v>-170000</v>
+        <v>-560000</v>
       </c>
       <c r="S14" t="n">
-        <v>66000</v>
+        <v>14000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대형 수주 공시가 확인되었으며, 이에 따른 주가 상승 기대감이 높음.</t>
+          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주', '공시']</t>
+          <t>['6G통신', '광통신', '데이터센터']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90400</v>
+        <v>8870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>236</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>912</v>
+        <v>289</v>
       </c>
       <c r="H15" t="n">
-        <v>23.59</v>
+        <v>27.19</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>89900</v>
+        <v>8950</v>
       </c>
       <c r="K15" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>91000</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>23.65</v>
+        <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>168910061100</v>
+        <v>18643000000</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-309000</v>
+        <v>-8000</v>
       </c>
       <c r="S15" t="n">
-        <v>77000</v>
+        <v>-241000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 에너지 투자 협상 타결 및 원전 사업 수주 기대감 부각. 대규모 수주 잔고와 연기금 매수세에 따른 상승 전망.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['에너지 협상', '원전 수주', '수주 잔고']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19800</v>
+        <v>89900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="F16" t="n">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="G16" t="n">
-        <v>550</v>
+        <v>925</v>
       </c>
       <c r="H16" t="n">
-        <v>10.65</v>
+        <v>23.59</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19750</v>
+        <v>91700</v>
       </c>
       <c r="K16" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>19960</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>19060</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>10.64</v>
+        <v>23.65</v>
       </c>
       <c r="O16" t="n">
-        <v>115236038310</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>28000</v>
+        <v>-313000</v>
       </c>
       <c r="S16" t="n">
-        <v>-44000</v>
+        <v>77000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차해지 관련 주주 독려와 목표가 상향 뉴스가 언급되었으나, 구체적인 근거는 부족함.</t>
+          <t>미국 에너지 투자 협상 타결 및 원전 사업 수주 기대감 부각. 대규모 수주 잔고와 연기금 매수세에 따른 상승 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '목표가']</t>
+          <t>['에너지 협상', '원전 수주', '수주 잔고']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1903</v>
+        <v>192900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="H17" t="n">
-        <v>2.44</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,183 +1975,183 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1901</v>
+        <v>197500</v>
       </c>
       <c r="K17" t="n">
-        <v>2050</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.12</v>
+        <v>75.92</v>
       </c>
       <c r="O17" t="n">
-        <v>43180854445</v>
+        <v>492494000000</v>
       </c>
       <c r="P17" t="n">
-        <v>4795</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1524</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-445000</v>
+        <v>-1193000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 급등 관련 전쟁 테마주로 분류되며, VLCC 용선료 폭등 소식이 전해지고 있음.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', 'VLCC', '유가']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>415000</v>
+        <v>7790</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-2.50%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="H18" t="n">
-        <v>38.02</v>
+        <v>0.52</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>415500</v>
+        <v>7990</v>
       </c>
       <c r="K18" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>418000</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>37.82</v>
+        <v>0.46</v>
       </c>
       <c r="O18" t="n">
-        <v>60755818250</v>
+        <v>87770000000</v>
       </c>
       <c r="P18" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>30000</v>
+        <v>14000</v>
       </c>
       <c r="S18" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
+          <t>594억 공급 계약 및 포스코 관련 사업 내용이 언급되나, 유통 물량 부족과 급등락에 대한 우려도 존재함.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['수주', '로봇', '미래차']</t>
+          <t>['공급계약', '포스코', '유통물량']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8870</v>
+        <v>51800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03</v>
+        <v>-0.44</v>
       </c>
       <c r="E19" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>286</v>
+        <v>199</v>
       </c>
       <c r="H19" t="n">
-        <v>27.19</v>
+        <v>2.92</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8970</v>
+        <v>53200</v>
       </c>
       <c r="K19" t="n">
-        <v>8780</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>8890</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>8680</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>27.16</v>
+        <v>3.36</v>
       </c>
       <c r="O19" t="n">
-        <v>18354578440</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-9000</v>
+        <v>127000</v>
       </c>
       <c r="S19" t="n">
-        <v>-243000</v>
+        <v>34000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['경영부진', '주가하락', '디스플레이']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14040</v>
+        <v>28750</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
-        <v>669</v>
+        <v>169</v>
       </c>
       <c r="H20" t="n">
-        <v>5.98</v>
+        <v>51.44</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>14320</v>
+        <v>29550</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>28650</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="N20" t="n">
-        <v>6.09</v>
+        <v>24.99</v>
       </c>
       <c r="O20" t="n">
-        <v>106864000000</v>
+        <v>51874080775</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>31200</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>599000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-270000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>자포리 원전 이슈 및 미국 원전 섹터 강세에 따른 기대감 형성. 모건스텐리 대규모 매수세 유입 및 120일선 지지선 중요성 강조. 원전 섹터 주도주 역할 기대.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '자포리', '모건스텐리']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,77 +2304,77 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14710</v>
+        <v>2095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>296</v>
+        <v>381</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15040</v>
+        <v>2160</v>
       </c>
       <c r="K21" t="n">
-        <v>14550</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>15260</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>14350</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>21183857475</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>19380</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>23000</v>
+        <v>219000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
+          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
+          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>065170</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>193000</v>
+        <v>1796000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.28%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>59</v>
+        <v>440</v>
       </c>
       <c r="G22" t="n">
-        <v>152</v>
+        <v>2048</v>
       </c>
       <c r="H22" t="n">
-        <v>75.98999999999999</v>
+        <v>50.55</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>197500</v>
+        <v>1856000</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>75.92</v>
+        <v>50.67</v>
       </c>
       <c r="O22" t="n">
-        <v>483725000000</v>
+        <v>3715324000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2459,67 +2459,67 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-1185000</v>
+        <v>-393000</v>
       </c>
       <c r="S22" t="n">
-        <v>-57000</v>
+        <v>-178000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>계단식 상승 기대감과 함께 초대형 호재 및 기관 매수세 언급이 있으나, CPI 발표와 유가 변동성이 주가에 영향을 줄 수 있음.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['반도체', '호재', '기관매수']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28700</v>
+        <v>15040</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>163</v>
+        <v>307</v>
       </c>
       <c r="H23" t="n">
-        <v>51.43</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,38 +2527,38 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>29550</v>
+        <v>15640</v>
       </c>
       <c r="K23" t="n">
-        <v>28650</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>28900</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>28500</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>24.99</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>50999976300</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>594000</v>
+        <v>23000</v>
       </c>
       <c r="S23" t="n">
-        <v>-269000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,77 +2580,77 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>비엘팜텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2095</v>
+        <v>258500</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.01%</t>
+          <t>-3.90%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E24" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>496</v>
       </c>
       <c r="G24" t="n">
-        <v>368</v>
+        <v>1771</v>
       </c>
       <c r="H24" t="n">
-        <v>1.32</v>
+        <v>46.71</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2160</v>
+        <v>269000</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>256500</v>
       </c>
       <c r="N24" t="n">
-        <v>1.36</v>
+        <v>46.81</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2807564695250</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R24" t="n">
-        <v>219000</v>
+        <v>-2983000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-1179000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
+          <t>이재명 재판 관련 정치적 요인과 반도체 시장 상황이 주가에 영향을 미칠 것이라는 의견이 있으나, 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,143 +2659,143 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
+          <t>['정치', '반도체', '주가']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>065170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1795500</v>
+        <v>12120</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-4.04%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.12</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
-        <v>800</v>
+        <v>108</v>
       </c>
       <c r="F25" t="n">
-        <v>439</v>
+        <v>51</v>
       </c>
       <c r="G25" t="n">
-        <v>1967</v>
+        <v>116</v>
       </c>
       <c r="H25" t="n">
-        <v>50.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1853000</v>
+        <v>12630</v>
       </c>
       <c r="K25" t="n">
-        <v>1773000</v>
+        <v>12520</v>
       </c>
       <c r="L25" t="n">
-        <v>1812000</v>
+        <v>12930</v>
       </c>
       <c r="M25" t="n">
-        <v>1768000</v>
+        <v>12010</v>
       </c>
       <c r="N25" t="n">
-        <v>50.67</v>
+        <v>0.14</v>
       </c>
       <c r="O25" t="n">
-        <v>3652592970000</v>
+        <v>64327719955</v>
       </c>
       <c r="P25" t="n">
-        <v>2987000</v>
+        <v>20850</v>
       </c>
       <c r="Q25" t="n">
-        <v>305500</v>
+        <v>4020</v>
       </c>
       <c r="R25" t="n">
-        <v>-389000</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-179000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>중동 평화 회담 선언 및 유가 하락 등 대외 변수에 영향을 받으며, 기관 매수세 유입에 따른 반등 기대감이 나타남.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['중동', '유가', '기관 매수']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14170</v>
+        <v>13930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.87%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.39</v>
+        <v>-0.11</v>
       </c>
       <c r="E26" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F26" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G26" t="n">
-        <v>428</v>
+        <v>680</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5</v>
+        <v>5.98</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,99 +2803,99 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>14740</v>
+        <v>14600</v>
       </c>
       <c r="K26" t="n">
-        <v>14050</v>
+        <v>14800</v>
       </c>
       <c r="L26" t="n">
-        <v>14560</v>
+        <v>14950</v>
       </c>
       <c r="M26" t="n">
-        <v>14030</v>
+        <v>13910</v>
       </c>
       <c r="N26" t="n">
-        <v>2.89</v>
+        <v>6.09</v>
       </c>
       <c r="O26" t="n">
-        <v>61245478140</v>
+        <v>112156179315</v>
       </c>
       <c r="P26" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q26" t="n">
-        <v>1272</v>
+        <v>3540</v>
       </c>
       <c r="R26" t="n">
-        <v>-303000</v>
+        <v>-236000</v>
       </c>
       <c r="S26" t="n">
-        <v>-28000</v>
+        <v>-163000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>광통신 섹터 내에서 대장주로 언급되며, 매수 기회를 주는 흐름 속에서 추가 상승에 대한 기대감이 나타나고 있음.</t>
+          <t>자포리 원전 이슈 및 미국 원전 섹터 강세에 따른 기대감 형성. 모건스텐리 대규모 매수세 유입 및 120일선 지지선 중요성 강조. 원전 섹터 주도주 역할 기대.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['광통신', '대장주', '매수세']</t>
+          <t>['원전', '자포리', '모건스텐리']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>259000</v>
+        <v>9280</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-3.90%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>800</v>
+        <v>76</v>
       </c>
       <c r="F27" t="n">
-        <v>497</v>
+        <v>43</v>
       </c>
       <c r="G27" t="n">
-        <v>1825</v>
+        <v>334</v>
       </c>
       <c r="H27" t="n">
-        <v>46.71</v>
+        <v>4.49</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>269500</v>
+        <v>9800</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>46.81</v>
+        <v>4.42</v>
       </c>
       <c r="O27" t="n">
-        <v>2760826000000</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2919,67 +2919,67 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-3107000</v>
+        <v>-88000</v>
       </c>
       <c r="S27" t="n">
-        <v>-1180000</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 하락하며, 반도체 섹터 전반의 약세와 함께 개별적인 이슈에 대한 언급이 혼재함.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '반도체', '하락']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9280</v>
+        <v>14140</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-5.48%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="E28" t="n">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="G28" t="n">
-        <v>334</v>
+        <v>441</v>
       </c>
       <c r="H28" t="n">
-        <v>4.49</v>
+        <v>2.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>9800</v>
+        <v>14960</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2999,10 +2999,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.42</v>
+        <v>2.89</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>62393000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3011,36 +3011,36 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-88000</v>
+        <v>-303000</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>-28000</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>정치적 요인과 금리 인상 관련 언급이 있으며, 우리로 종목과의 비교 및 매수 기회에 대한 논의가 있음.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['정치', '금리', '매수']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -3051,24 +3051,24 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7700</v>
+        <v>7790</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-7.23%</t>
+          <t>-6.14%</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0.12</v>
       </c>
       <c r="E29" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F29" t="n">
         <v>107</v>
       </c>
       <c r="G29" t="n">
-        <v>1179</v>
+        <v>1218</v>
       </c>
       <c r="H29" t="n">
         <v>1.29</v>
@@ -3094,7 +3094,7 @@
         <v>1.17</v>
       </c>
       <c r="O29" t="n">
-        <v>29755516175</v>
+        <v>30174618330</v>
       </c>
       <c r="P29" t="n">
         <v>21500</v>
@@ -3110,16 +3110,16 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>9월 14일 세계폐암학회(WCLC)에서의 데이터 발표를 앞두고 주가 급등 예고 및 기대감이 형성되고 있으며, 외국계 증권사 유입 소식이 있음.</t>
+          <t>9월 14일 WCLC 학회에서의 데이터 발표에 대한 기대감이 높으며, 관련 임상 시험 및 외인 수급에 대한 언급이 있음.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['임상시험', 'WCLC', '데이터 발표']</t>
+          <t>['임상시험', 'WCLC', '데이터']</t>
         </is>
       </c>
       <c r="X29" t="n">
@@ -3139,31 +3139,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12070</v>
+        <v>3550</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-7.37%</t>
+          <t>-8.15%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="F30" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G30" t="n">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>13030</v>
+        <v>3865</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3183,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.14</v>
+        <v>1.54</v>
       </c>
       <c r="O30" t="n">
-        <v>64057000000</v>
+        <v>47870000000</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -3195,14 +3195,14 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>-105000</v>
+        <v>-110000</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -3211,11 +3211,11 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '거래량']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3224,38 +3224,38 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3570</v>
+        <v>26400</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-7.63%</t>
+          <t>-12.87%</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E31" t="n">
-        <v>69</v>
+        <v>334</v>
       </c>
       <c r="F31" t="n">
-        <v>41</v>
+        <v>162</v>
       </c>
       <c r="G31" t="n">
-        <v>160</v>
+        <v>536</v>
       </c>
       <c r="H31" t="n">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>3865</v>
+        <v>30300</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3275,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.54</v>
+        <v>0.33</v>
       </c>
       <c r="O31" t="n">
-        <v>47493000000</v>
+        <v>333036000000</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3287,14 +3287,14 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>주가 하락에 대한 부정적 심리가 강하며, 명확한 사실 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -3303,20 +3303,20 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>386380</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_14.xlsx
+++ b/data/trending_integrated_20260911_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>208210837225</v>
+        <v>208277181085</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -619,23 +619,23 @@
         <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-71000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 지목과 함께, 양자 보안 기술 상용화 및 공급 계약 소식이 부각되며 강한 상승세를 보임.</t>
+          <t>세계 최초 양자 보안 기술 상용화 성공 및 젠슨 황 발언 기반 사이버 보안 섹터 급등.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버 보안', '양자 보안', '젠슨 황']</t>
+          <t>['양자보안', '사이버보안', '젠슨황']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15090</v>
+        <v>2655</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+24.81%</t>
+          <t>+24.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>457</v>
+        <v>133</v>
       </c>
       <c r="F3" t="n">
-        <v>253</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
-        <v>999</v>
+        <v>222</v>
       </c>
       <c r="H3" t="n">
-        <v>3.14</v>
+        <v>3.83</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12090</v>
+        <v>2125</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2725</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>208057000000</v>
+        <v>119577507120</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R3" t="n">
-        <v>-339000</v>
+        <v>-1952000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
+          <t>미국 정부 양자컴퓨터 보조금 지원 체결 뉴스 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁 테마', 'WTI']</t>
+          <t>['양자컴퓨터', '보조금']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2640</v>
+        <v>15940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+23.65%</t>
+          <t>+21.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="E4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F4" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="H4" t="n">
-        <v>3.83</v>
+        <v>1.24</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2135</v>
+        <v>13160</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>12910</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>16920</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>12910</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
-        <v>117296000000</v>
+        <v>167547981385</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>61700</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="R4" t="n">
-        <v>-1952000</v>
+        <v>6000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>거래량은 높으나 주가 상승 동력이 부족하다는 의견과 함께, 미국 정부의 양자컴퓨터 보조금 지원 뉴스가 언급됨.</t>
+          <t>K-뷰티 대장주 등극 기대감과 함께 소규모 매수세 유입.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['거래량', '양자컴퓨터', '주가']</t>
+          <t>['K-뷰티', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16190</v>
+        <v>138300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.36%</t>
+          <t>+19.53%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.19</v>
+        <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="G5" t="n">
-        <v>185</v>
+        <v>339</v>
       </c>
       <c r="H5" t="n">
-        <v>1.24</v>
+        <v>4.32</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13340</v>
+        <v>115700</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N5" t="n">
-        <v>1.43</v>
+        <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>164937000000</v>
+        <v>501099523050</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R5" t="n">
-        <v>6000</v>
+        <v>39000</v>
       </c>
       <c r="S5" t="n">
-        <v>115000</v>
+        <v>118000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>K-뷰티 관련 기대감 속에서 일부 상승 흐름이 있으나, 추격 매수 및 단기 이익 실현에 대한 언급도 공존함.</t>
+          <t>제품 품절 이슈와 함께 애플 관련 상승 기대감 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['K-뷰티', '상승세', '추격매수']</t>
+          <t>['거래량', '애플']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137200</v>
+        <v>7680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+17.97%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.26</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>331</v>
+        <v>497</v>
       </c>
       <c r="H6" t="n">
-        <v>4.32</v>
+        <v>11.72</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>116300</v>
+        <v>7100</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.58</v>
+        <v>11.62</v>
       </c>
       <c r="O6" t="n">
-        <v>493408000000</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -987,27 +987,27 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>39000</v>
+        <v>45000</v>
       </c>
       <c r="S6" t="n">
-        <v>118000</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>폭발적인 거래량 동반 상승세에 대한 기대감이 있으나, 급격한 상승 후 매물 소화 및 추가 상승 여부에 대한 관망세가 나타남.</t>
+          <t>뉴스 기반 주가 상승 기대와 함께 개인 투자자의 자금 이탈 및 기관 매수 가능성에 대한 언급이 혼재되어 있음.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['거래량', '상승', '매물 소화']</t>
+          <t>['주가 상승', '기관 매수', '개인 투자자']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7280</v>
+        <v>9980</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.66%</t>
+          <t>+7.54%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.79</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>370</v>
+        <v>329</v>
       </c>
       <c r="H7" t="n">
-        <v>2.15</v>
+        <v>4.49</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6700</v>
+        <v>9280</v>
       </c>
       <c r="K7" t="n">
-        <v>6530</v>
+        <v>10030</v>
       </c>
       <c r="L7" t="n">
-        <v>8370</v>
+        <v>10880</v>
       </c>
       <c r="M7" t="n">
-        <v>6430</v>
+        <v>9800</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>4.42</v>
       </c>
       <c r="O7" t="n">
-        <v>168372621110</v>
+        <v>21987597455</v>
       </c>
       <c r="P7" t="n">
-        <v>16200</v>
+        <v>15640</v>
       </c>
       <c r="Q7" t="n">
-        <v>1206</v>
+        <v>5470</v>
       </c>
       <c r="R7" t="n">
-        <v>170000</v>
+        <v>-88000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>광통신 및 위성 네트워크 관련 펀드 편입 소식이 있으며, 대장주로서의 역할과 공매도 감소에 대한 기대감이 공존함.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '펀드', '공매도']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,82 +1103,82 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7680</v>
+        <v>7200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+7.46%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>-0.79</v>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G8" t="n">
-        <v>483</v>
+        <v>378</v>
       </c>
       <c r="H8" t="n">
-        <v>11.72</v>
+        <v>2.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7100</v>
+        <v>6700</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6530</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>8370</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6430</v>
       </c>
       <c r="N8" t="n">
-        <v>11.62</v>
+        <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>170489806095</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R8" t="n">
-        <v>45000</v>
+        <v>170000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>뉴스 기반 주가 상승 기대와 함께 개인 투자자의 자금 이탈 및 기관 매수 가능성에 대한 언급이 혼재되어 있음.</t>
+          <t>광통신 및 위성 네트워크 관련 펀드 편입 소식이 있으며, 대장주로서의 역할과 공매도 감소에 대한 기대감이 공존함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 상승', '기관 매수', '개인 투자자']</t>
+          <t>['광통신', '펀드', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253000</v>
+        <v>14980</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+3.24%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.96</v>
+        <v>3.11</v>
       </c>
       <c r="E9" t="n">
-        <v>246</v>
+        <v>463</v>
       </c>
       <c r="F9" t="n">
-        <v>120</v>
+        <v>255</v>
       </c>
       <c r="G9" t="n">
-        <v>860</v>
+        <v>1013</v>
       </c>
       <c r="H9" t="n">
-        <v>7.58</v>
+        <v>3.14</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>250500</v>
+        <v>14510</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>17010</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>17310</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>14840</v>
       </c>
       <c r="N9" t="n">
-        <v>8.539999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>209092899165</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>36200</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>8920</v>
       </c>
       <c r="R9" t="n">
-        <v>-485000</v>
+        <v>-339000</v>
       </c>
       <c r="S9" t="n">
-        <v>-43000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>9월 TC본더 수출 데이터 및 공매도 관련 논의가 활발하며, 주가 하락에 대한 우려와 함께 기관 매수세가 언급됨.</t>
+          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['TC본더', '공매도', '기관']</t>
+          <t>['국제유가', '전쟁 테마', 'WTI']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50700</v>
+        <v>19950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+2.57%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G10" t="n">
-        <v>627</v>
+        <v>568</v>
       </c>
       <c r="H10" t="n">
-        <v>38.78</v>
+        <v>10.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>50400</v>
+        <v>19450</v>
       </c>
       <c r="K10" t="n">
-        <v>50500</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>51200</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>49650</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>38.69</v>
+        <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>73128452875</v>
+        <v>126974000000</v>
       </c>
       <c r="P10" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-172000</v>
+        <v>28000</v>
       </c>
       <c r="S10" t="n">
-        <v>64000</v>
+        <v>-43000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대형 수주 공시가 확인되었으며, 이에 따른 주가 상승 기대감이 높음.</t>
+          <t>대차해지 요청과 함께 공매도 관련 논의가 활발하며, 목표가 상향 및 원전 투자 관련 뉴스가 언급됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '공시']</t>
+          <t>['대차해지', '공매도', '원전']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,86 +1384,86 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1903</v>
+        <v>7800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="H11" t="n">
-        <v>2.44</v>
+        <v>0.52</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1901</v>
+        <v>7690</v>
       </c>
       <c r="K11" t="n">
-        <v>2050</v>
+        <v>7670</v>
       </c>
       <c r="L11" t="n">
-        <v>2080</v>
+        <v>9170</v>
       </c>
       <c r="M11" t="n">
-        <v>1900</v>
+        <v>7450</v>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>0.46</v>
       </c>
       <c r="O11" t="n">
-        <v>43346852950</v>
+        <v>88107479415</v>
       </c>
       <c r="P11" t="n">
-        <v>4795</v>
+        <v>9170</v>
       </c>
       <c r="Q11" t="n">
-        <v>1524</v>
+        <v>3720</v>
       </c>
       <c r="R11" t="n">
-        <v>-445000</v>
+        <v>14000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 급등 관련 전쟁 테마주로 분류되며, VLCC 용선료 폭등 소식이 전해지고 있음.</t>
+          <t>594억 공급 계약 및 포스코 관련 사업 내용이 언급되나, 유통 물량 부족과 급등락에 대한 우려도 존재함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', 'VLCC', '유가']</t>
+          <t>['공급계약', '포스코', '유통물량']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19770</v>
+        <v>51000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+1.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="F12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G12" t="n">
-        <v>557</v>
+        <v>629</v>
       </c>
       <c r="H12" t="n">
-        <v>10.65</v>
+        <v>38.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>19750</v>
+        <v>50400</v>
       </c>
       <c r="K12" t="n">
-        <v>19500</v>
+        <v>50500</v>
       </c>
       <c r="L12" t="n">
-        <v>19960</v>
+        <v>51200</v>
       </c>
       <c r="M12" t="n">
-        <v>19060</v>
+        <v>49650</v>
       </c>
       <c r="N12" t="n">
-        <v>10.64</v>
+        <v>38.69</v>
       </c>
       <c r="O12" t="n">
-        <v>117515780985</v>
+        <v>74338188975</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>28000</v>
+        <v>-172000</v>
       </c>
       <c r="S12" t="n">
-        <v>-43000</v>
+        <v>64000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대차해지 요청과 함께 공매도 관련 논의가 활발하며, 목표가 상향 및 원전 투자 관련 뉴스가 언급됨.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시가 확인되었으며, 이에 따른 주가 상승 기대감이 높음.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '원전']</t>
+          <t>['수주', '공시']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>415500</v>
+        <v>52300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>-0.44</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>289</v>
+        <v>201</v>
       </c>
       <c r="H13" t="n">
-        <v>38.02</v>
+        <v>2.92</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>415500</v>
+        <v>51800</v>
       </c>
       <c r="K13" t="n">
-        <v>407000</v>
+        <v>51300</v>
       </c>
       <c r="L13" t="n">
-        <v>418000</v>
+        <v>54500</v>
       </c>
       <c r="M13" t="n">
-        <v>404000</v>
+        <v>51300</v>
       </c>
       <c r="N13" t="n">
-        <v>37.82</v>
+        <v>3.36</v>
       </c>
       <c r="O13" t="n">
-        <v>62130264750</v>
+        <v>103842912100</v>
       </c>
       <c r="P13" t="n">
-        <v>822000</v>
+        <v>87700</v>
       </c>
       <c r="Q13" t="n">
-        <v>283000</v>
+        <v>17210</v>
       </c>
       <c r="R13" t="n">
-        <v>31000</v>
+        <v>127000</v>
       </c>
       <c r="S13" t="n">
-        <v>5000</v>
+        <v>34000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '로봇', '미래차']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3905</v>
+        <v>26350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.53</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>342</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="G14" t="n">
-        <v>209</v>
+        <v>540</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>0.32</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3925</v>
+        <v>26100</v>
       </c>
       <c r="K14" t="n">
-        <v>3810</v>
+        <v>26350</v>
       </c>
       <c r="L14" t="n">
-        <v>4180</v>
+        <v>30300</v>
       </c>
       <c r="M14" t="n">
-        <v>3760</v>
+        <v>25400</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>0.33</v>
       </c>
       <c r="O14" t="n">
-        <v>94443945730</v>
+        <v>334161249225</v>
       </c>
       <c r="P14" t="n">
-        <v>8100</v>
+        <v>39350</v>
       </c>
       <c r="Q14" t="n">
-        <v>592</v>
+        <v>8200</v>
       </c>
       <c r="R14" t="n">
-        <v>-560000</v>
+        <v>2000</v>
       </c>
       <c r="S14" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
+          <t>주가 하락에 대한 부정적 심리가 강하며, 명확한 사실 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,51 +1739,51 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['6G통신', '광통신', '데이터센터']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8870</v>
+        <v>90700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="G15" t="n">
-        <v>289</v>
+        <v>950</v>
       </c>
       <c r="H15" t="n">
-        <v>27.19</v>
+        <v>23.59</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8950</v>
+        <v>89900</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>91000</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="N15" t="n">
-        <v>27.16</v>
+        <v>23.65</v>
       </c>
       <c r="O15" t="n">
-        <v>18643000000</v>
+        <v>175969670750</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-8000</v>
+        <v>-313000</v>
       </c>
       <c r="S15" t="n">
-        <v>-241000</v>
+        <v>77000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
+          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 29조 7천억 규모 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['경영부진', '주가하락', '디스플레이']</t>
+          <t>['에너지', '수주잔고', '원전']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>89900</v>
+        <v>1899</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.06</v>
+        <v>0.32</v>
       </c>
       <c r="E16" t="n">
-        <v>239</v>
+        <v>130</v>
       </c>
       <c r="F16" t="n">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>925</v>
+        <v>261</v>
       </c>
       <c r="H16" t="n">
-        <v>23.59</v>
+        <v>2.44</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>91700</v>
+        <v>1901</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1899</v>
       </c>
       <c r="N16" t="n">
-        <v>23.65</v>
+        <v>2.12</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>43701509725</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4795</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="R16" t="n">
-        <v>-313000</v>
+        <v>-445000</v>
       </c>
       <c r="S16" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 에너지 투자 협상 타결 및 원전 사업 수주 기대감 부각. 대규모 수주 잔고와 연기금 매수세에 따른 상승 전망.</t>
+          <t>홍해 사태 및 유가 급등 관련 전쟁 테마주로 분류되며, VLCC 용선료 폭등 소식이 전해지고 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['에너지 협상', '원전 수주', '수주 잔고']</t>
+          <t>['전쟁 테마주', 'VLCC', '유가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>192900</v>
+        <v>415000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>160</v>
+        <v>291</v>
       </c>
       <c r="H17" t="n">
-        <v>75.98999999999999</v>
+        <v>38.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>197500</v>
+        <v>415500</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N17" t="n">
-        <v>75.92</v>
+        <v>37.82</v>
       </c>
       <c r="O17" t="n">
-        <v>492494000000</v>
+        <v>63849951500</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R17" t="n">
-        <v>-1193000</v>
+        <v>31000</v>
       </c>
       <c r="S17" t="n">
-        <v>-48000</v>
+        <v>5000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['수주', '로봇', '미래차']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7790</v>
+        <v>3910</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.50%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.53</v>
       </c>
       <c r="E18" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="H18" t="n">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7990</v>
+        <v>3925</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3810</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4180</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3760</v>
       </c>
       <c r="N18" t="n">
-        <v>0.46</v>
+        <v>1.57</v>
       </c>
       <c r="O18" t="n">
-        <v>87770000000</v>
+        <v>95273906583</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="R18" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>594억 공급 계약 및 포스코 관련 사업 내용이 언급되나, 유통 물량 부족과 급등락에 대한 우려도 존재함.</t>
+          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공급계약', '포스코', '유통물량']</t>
+          <t>['6G통신', '광통신', '데이터센터']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51800</v>
+        <v>29550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="H19" t="n">
-        <v>2.92</v>
+        <v>25.55</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>53200</v>
+        <v>29800</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.36</v>
+        <v>24.99</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2183,14 +2183,14 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>127000</v>
+        <v>599000</v>
       </c>
       <c r="S19" t="n">
-        <v>34000</v>
+        <v>-270000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28750</v>
+        <v>8880</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>169</v>
+        <v>290</v>
       </c>
       <c r="H20" t="n">
-        <v>51.44</v>
+        <v>27.19</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29550</v>
+        <v>8970</v>
       </c>
       <c r="K20" t="n">
-        <v>28650</v>
+        <v>8780</v>
       </c>
       <c r="L20" t="n">
-        <v>28900</v>
+        <v>8890</v>
       </c>
       <c r="M20" t="n">
-        <v>28500</v>
+        <v>8680</v>
       </c>
       <c r="N20" t="n">
-        <v>24.99</v>
+        <v>27.16</v>
       </c>
       <c r="O20" t="n">
-        <v>51874080775</v>
+        <v>18938907965</v>
       </c>
       <c r="P20" t="n">
-        <v>31200</v>
+        <v>17950</v>
       </c>
       <c r="Q20" t="n">
-        <v>21000</v>
+        <v>8120</v>
       </c>
       <c r="R20" t="n">
-        <v>599000</v>
+        <v>-8000</v>
       </c>
       <c r="S20" t="n">
-        <v>-270000</v>
+        <v>-241000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,77 +2304,77 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>비엘팜텍</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2095</v>
+        <v>14820</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.01%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>381</v>
+        <v>317</v>
       </c>
       <c r="H21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2160</v>
+        <v>15040</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>14550</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>15260</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>14350</v>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>21908447530</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>219000</v>
+        <v>23000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>065170</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1796000</v>
+        <v>1803000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.23%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G22" t="n">
-        <v>2048</v>
+        <v>2066</v>
       </c>
       <c r="H22" t="n">
         <v>50.55</v>
@@ -2450,7 +2450,7 @@
         <v>50.67</v>
       </c>
       <c r="O22" t="n">
-        <v>3715324000000</v>
+        <v>3790074000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>계단식 상승 기대감과 함께 초대형 호재 및 기관 매수세 언급이 있으나, CPI 발표와 유가 변동성이 주가에 영향을 줄 수 있음.</t>
+          <t>중동 평화 회담 관련 호재와 함께 기관 매수세 유입, 상승 추세 지속 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체', '호재', '기관매수']</t>
+          <t>['중동', '기관 매수', '추세']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,39 +2495,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15040</v>
+        <v>2095</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>307</v>
+        <v>397</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>15640</v>
+        <v>2160</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2551,14 +2551,14 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>23000</v>
+        <v>219000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
+          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
+          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>065170</t>
         </is>
       </c>
     </row>
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>258500</v>
+        <v>259500</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.90%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2605,10 +2605,10 @@
         <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G24" t="n">
-        <v>1771</v>
+        <v>1793</v>
       </c>
       <c r="H24" t="n">
         <v>46.71</v>
@@ -2634,7 +2634,7 @@
         <v>46.81</v>
       </c>
       <c r="O24" t="n">
-        <v>2807564695250</v>
+        <v>2870071698000</v>
       </c>
       <c r="P24" t="n">
         <v>374500</v>
@@ -2679,31 +2679,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12120</v>
+        <v>14150</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.04%</t>
+          <t>-4.00%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>-0.39</v>
       </c>
       <c r="E25" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="F25" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G25" t="n">
-        <v>116</v>
+        <v>443</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,91 +2711,91 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12630</v>
+        <v>14740</v>
       </c>
       <c r="K25" t="n">
-        <v>12520</v>
+        <v>14050</v>
       </c>
       <c r="L25" t="n">
-        <v>12930</v>
+        <v>14560</v>
       </c>
       <c r="M25" t="n">
-        <v>12010</v>
+        <v>14030</v>
       </c>
       <c r="N25" t="n">
-        <v>0.14</v>
+        <v>2.89</v>
       </c>
       <c r="O25" t="n">
-        <v>64327719955</v>
+        <v>63203703155</v>
       </c>
       <c r="P25" t="n">
-        <v>20850</v>
+        <v>31500</v>
       </c>
       <c r="Q25" t="n">
-        <v>4020</v>
+        <v>1272</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>-303000</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-28000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
+          <t>정치적 요인과 금리 인상 관련 언급이 있으며, 우리로 종목과의 비교 및 매수 기회에 대한 논의가 있음.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '거래량']</t>
+          <t>['정치', '금리', '매수']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13930</v>
+        <v>12100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>-4.20%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.11</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F26" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G26" t="n">
-        <v>680</v>
+        <v>116</v>
       </c>
       <c r="H26" t="n">
-        <v>5.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,38 +2803,38 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>14600</v>
+        <v>12630</v>
       </c>
       <c r="K26" t="n">
-        <v>14800</v>
+        <v>12520</v>
       </c>
       <c r="L26" t="n">
-        <v>14950</v>
+        <v>12930</v>
       </c>
       <c r="M26" t="n">
-        <v>13910</v>
+        <v>12010</v>
       </c>
       <c r="N26" t="n">
-        <v>6.09</v>
+        <v>0.14</v>
       </c>
       <c r="O26" t="n">
-        <v>112156179315</v>
+        <v>64539238140</v>
       </c>
       <c r="P26" t="n">
-        <v>30200</v>
+        <v>20850</v>
       </c>
       <c r="Q26" t="n">
-        <v>3540</v>
+        <v>4020</v>
       </c>
       <c r="R26" t="n">
-        <v>-236000</v>
+        <v>-105000</v>
       </c>
       <c r="S26" t="n">
-        <v>-163000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>자포리 원전 이슈 및 미국 원전 섹터 강세에 따른 기대감 형성. 모건스텐리 대규모 매수세 유입 및 120일선 지지선 중요성 강조. 원전 섹터 주도주 역할 기대.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['원전', '자포리', '모건스텐리']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,38 +2856,38 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9280</v>
+        <v>13980</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E27" t="n">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="G27" t="n">
-        <v>334</v>
+        <v>688</v>
       </c>
       <c r="H27" t="n">
-        <v>4.49</v>
+        <v>5.98</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,91 +2895,91 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>9800</v>
+        <v>14600</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>14950</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>13910</v>
       </c>
       <c r="N27" t="n">
-        <v>4.42</v>
+        <v>6.09</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>113761926805</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3540</v>
       </c>
       <c r="R27" t="n">
-        <v>-88000</v>
+        <v>-236000</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-163000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>원전 관련 이슈 속 모건 스탠리 매도 물량 출회, 단기 과열 가능성 언급.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['원전', '모건스탠리']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14140</v>
+        <v>7910</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-5.48%</t>
+          <t>-4.70%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.39</v>
+        <v>0.12</v>
       </c>
       <c r="E28" t="n">
-        <v>122</v>
+        <v>257</v>
       </c>
       <c r="F28" t="n">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="G28" t="n">
-        <v>441</v>
+        <v>1261</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2987,51 +2987,51 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>14960</v>
+        <v>8300</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="N28" t="n">
-        <v>2.89</v>
+        <v>1.17</v>
       </c>
       <c r="O28" t="n">
-        <v>62393000000</v>
+        <v>30489422015</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="R28" t="n">
-        <v>-303000</v>
+        <v>-183000</v>
       </c>
       <c r="S28" t="n">
-        <v>-28000</v>
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>정치적 요인과 금리 인상 관련 언급이 있으며, 우리로 종목과의 비교 및 매수 기회에 대한 논의가 있음.</t>
+          <t>9월 14일 WCLC 학회 센딥파텔 교수 데이터 발표 기반 주가 대폭등 예고.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['정치', '금리', '매수']</t>
+          <t>['WCLC', '폐암학회', '데이터']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3040,222 +3040,222 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7790</v>
+        <v>193100</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-6.14%</t>
+          <t>-4.88%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>252</v>
+        <v>94</v>
       </c>
       <c r="F29" t="n">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="G29" t="n">
-        <v>1218</v>
+        <v>161</v>
       </c>
       <c r="H29" t="n">
-        <v>1.29</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>8300</v>
+        <v>203000</v>
       </c>
       <c r="K29" t="n">
-        <v>8400</v>
+        <v>195000</v>
       </c>
       <c r="L29" t="n">
-        <v>8700</v>
+        <v>195600</v>
       </c>
       <c r="M29" t="n">
-        <v>7540</v>
+        <v>191000</v>
       </c>
       <c r="N29" t="n">
-        <v>1.17</v>
+        <v>75.92</v>
       </c>
       <c r="O29" t="n">
-        <v>30174618330</v>
+        <v>504003529650</v>
       </c>
       <c r="P29" t="n">
-        <v>21500</v>
+        <v>243500</v>
       </c>
       <c r="Q29" t="n">
-        <v>2300</v>
+        <v>58600</v>
       </c>
       <c r="R29" t="n">
-        <v>-183000</v>
+        <v>-1193000</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>9월 14일 WCLC 학회에서의 데이터 발표에 대한 기대감이 높으며, 관련 임상 시험 및 외인 수급에 대한 언급이 있음.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['임상시험', 'WCLC', '데이터']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3550</v>
+        <v>232500</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-8.15%</t>
+          <t>-8.10%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.96</v>
       </c>
       <c r="E30" t="n">
-        <v>69</v>
+        <v>254</v>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="G30" t="n">
-        <v>161</v>
+        <v>871</v>
       </c>
       <c r="H30" t="n">
-        <v>0.73</v>
+        <v>7.58</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3865</v>
+        <v>253000</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="N30" t="n">
-        <v>1.54</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>47870000000</v>
+        <v>213485181500</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>86100</v>
       </c>
       <c r="R30" t="n">
-        <v>-110000</v>
+        <v>-485000</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>-43000</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>9월 TC본더 수출 데이터 및 공매도 관련 논의가 활발하며, 주가 하락에 대한 우려와 함께 기관 매수세가 언급됨.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['TC본더', '공매도', '기관']</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26400</v>
+        <v>3550</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-12.87%</t>
+          <t>-8.15%</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.01</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>334</v>
+        <v>69</v>
       </c>
       <c r="F31" t="n">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="G31" t="n">
-        <v>536</v>
+        <v>161</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32</v>
+        <v>0.73</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>30300</v>
+        <v>3865</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3275,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.33</v>
+        <v>1.54</v>
       </c>
       <c r="O31" t="n">
-        <v>333036000000</v>
+        <v>48216000000</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3287,14 +3287,14 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2000</v>
+        <v>-110000</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 부정적 심리가 강하며, 명확한 사실 기반 분석은 부족함.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -3303,20 +3303,20 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>067290</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_14.xlsx
+++ b/data/trending_integrated_20260911_14.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16060</v>
+        <v>2720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.94%</t>
+          <t>+29.83%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.22</v>
+        <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>171</v>
+        <v>402</v>
       </c>
       <c r="H2" t="n">
-        <v>2.39</v>
+        <v>1.32</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12360</v>
+        <v>2095</v>
       </c>
       <c r="K2" t="n">
-        <v>12800</v>
+        <v>2090</v>
       </c>
       <c r="L2" t="n">
-        <v>16060</v>
+        <v>2720</v>
       </c>
       <c r="M2" t="n">
-        <v>12690</v>
+        <v>2080</v>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
-        <v>208277181085</v>
+        <v>8137878164</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>8150</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>376</v>
       </c>
       <c r="R2" t="n">
-        <v>-71000</v>
+        <v>219000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>세계 최초 양자 보안 기술 상용화 성공 및 젠슨 황 발언 기반 사이버 보안 섹터 급등.</t>
+          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자보안', '사이버보안', '젠슨황']</t>
+          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,43 +643,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>065170</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2655</v>
+        <v>16060</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+24.94%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="H3" t="n">
-        <v>3.83</v>
+        <v>2.39</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2125</v>
+        <v>12610</v>
       </c>
       <c r="K3" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2725</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.76</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>119577507120</v>
+        <v>208336000000</v>
       </c>
       <c r="P3" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-1952000</v>
+        <v>-71000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 정부 양자컴퓨터 보조금 지원 체결 뉴스 기반 상승 기대.</t>
+          <t>젠슨 황 발언에 따른 AI 보안 테마로 급등. 양자 보안 기술 상용화 성공 및 공급 계약, 기관 매집 근거.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보조금']</t>
+          <t>['AI 보안', '양자 보안', '젠슨 황']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15940</v>
+        <v>2635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.12%</t>
+          <t>+23.42%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G4" t="n">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="H4" t="n">
-        <v>1.24</v>
+        <v>3.83</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13160</v>
+        <v>2135</v>
       </c>
       <c r="K4" t="n">
-        <v>12910</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>16920</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>12910</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.43</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>167547981385</v>
+        <v>121709000000</v>
       </c>
       <c r="P4" t="n">
-        <v>61700</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>K-뷰티 대장주 등극 기대감과 함께 소규모 매수세 유입.</t>
+          <t>거래량 대비 주가 상승력 부족 및 외인 매도세 관찰. 테마 시작 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['K-뷰티', '대장주']</t>
+          <t>['거래량', '외인 매도', '테마 시작']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>138300</v>
+        <v>14880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+19.53%</t>
+          <t>+23.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.26</v>
+        <v>3.11</v>
       </c>
       <c r="E5" t="n">
-        <v>156</v>
+        <v>476</v>
       </c>
       <c r="F5" t="n">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="G5" t="n">
-        <v>339</v>
+        <v>1022</v>
       </c>
       <c r="H5" t="n">
-        <v>4.32</v>
+        <v>3.14</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>115700</v>
+        <v>12090</v>
       </c>
       <c r="K5" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.58</v>
+        <v>0.03</v>
       </c>
       <c r="O5" t="n">
-        <v>501099523050</v>
+        <v>210397000000</v>
       </c>
       <c r="P5" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>39000</v>
+        <v>-339000</v>
       </c>
       <c r="S5" t="n">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>제품 품절 이슈와 함께 애플 관련 상승 기대감 존재.</t>
+          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['거래량', '애플']</t>
+          <t>['국제 유가', '전쟁 테마주', 'WTI 100달러']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7680</v>
+        <v>15820</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+20.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="E6" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
-        <v>497</v>
+        <v>194</v>
       </c>
       <c r="H6" t="n">
-        <v>11.72</v>
+        <v>1.24</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7100</v>
+        <v>13160</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>12910</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>16920</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>12910</v>
       </c>
       <c r="N6" t="n">
-        <v>11.62</v>
+        <v>1.43</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>171215654825</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>61700</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="R6" t="n">
-        <v>45000</v>
+        <v>6000</v>
       </c>
       <c r="S6" t="n">
-        <v>1000</v>
+        <v>115000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뉴스 기반 주가 상승 기대와 함께 개인 투자자의 자금 이탈 및 기관 매수 가능성에 대한 언급이 혼재되어 있음.</t>
+          <t>K-뷰티 대장주로서의 기대감과 함께 급등세 지속. 경영권 및 금리 인상 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 상승', '기관 매수', '개인 투자자']</t>
+          <t>['K-뷰티', '급등세', '경영권']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,99 +1016,99 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9980</v>
+        <v>137100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.54%</t>
+          <t>+18.50%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="G7" t="n">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="H7" t="n">
-        <v>4.49</v>
+        <v>4.32</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9280</v>
+        <v>115700</v>
       </c>
       <c r="K7" t="n">
-        <v>10030</v>
+        <v>112100</v>
       </c>
       <c r="L7" t="n">
-        <v>10880</v>
+        <v>147500</v>
       </c>
       <c r="M7" t="n">
-        <v>9800</v>
+        <v>112000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.42</v>
+        <v>4.58</v>
       </c>
       <c r="O7" t="n">
-        <v>21987597455</v>
+        <v>508459885900</v>
       </c>
       <c r="P7" t="n">
-        <v>15640</v>
+        <v>196800</v>
       </c>
       <c r="Q7" t="n">
-        <v>5470</v>
+        <v>27750</v>
       </c>
       <c r="R7" t="n">
-        <v>-88000</v>
+        <v>39000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>높은 상승률과 함께 '물건이 없어서 못 판다'는 언급. 거래량 부족 및 고점 매수 경계.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['상승률', '거래량', '매수 경계']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7200</v>
+        <v>7180</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.46%</t>
+          <t>+9.28%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.79</v>
       </c>
       <c r="E8" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G8" t="n">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="H8" t="n">
         <v>2.15</v>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6700</v>
+        <v>6570</v>
       </c>
       <c r="K8" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>170489806095</v>
+        <v>171846000000</v>
       </c>
       <c r="P8" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>170000</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>광통신 및 위성 네트워크 관련 펀드 편입 소식이 있으며, 대장주로서의 역할과 공매도 감소에 대한 기대감이 공존함.</t>
+          <t>광통신 및 위성 네트워크 관련 테마주로 부각. 현재 주가 상승력 부족 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '펀드', '공매도']</t>
+          <t>['광통신', '위성 네트워크', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14980</v>
+        <v>1898</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3.24%</t>
+          <t>+7.84%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.11</v>
+        <v>0.32</v>
       </c>
       <c r="E9" t="n">
-        <v>463</v>
+        <v>130</v>
       </c>
       <c r="F9" t="n">
-        <v>255</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>1013</v>
+        <v>256</v>
       </c>
       <c r="H9" t="n">
-        <v>3.14</v>
+        <v>2.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14510</v>
+        <v>1760</v>
       </c>
       <c r="K9" t="n">
-        <v>17010</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>17310</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>14840</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>209092899165</v>
+        <v>44010000000</v>
       </c>
       <c r="P9" t="n">
-        <v>36200</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8920</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-339000</v>
+        <v>-445000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
+          <t>홍해 사태 및 유가 급등으로 인한 전쟁 테마주로서의 부각. VLCC 부유식 저장고 용선료 폭등 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁 테마', 'WTI']</t>
+          <t>['홍해 사태', '전쟁 테마주', '유가 급등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,46 +1292,46 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19950</v>
+        <v>7990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.57%</t>
+          <t>+7.68%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>156</v>
+        <v>264</v>
       </c>
       <c r="F10" t="n">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G10" t="n">
-        <v>568</v>
+        <v>1313</v>
       </c>
       <c r="H10" t="n">
-        <v>10.65</v>
+        <v>1.29</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19450</v>
+        <v>7420</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10.64</v>
+        <v>1.17</v>
       </c>
       <c r="O10" t="n">
-        <v>126974000000</v>
+        <v>31093000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1355,27 +1355,27 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>28000</v>
+        <v>-183000</v>
       </c>
       <c r="S10" t="n">
-        <v>-43000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차해지 요청과 함께 공매도 관련 논의가 활발하며, 목표가 상향 및 원전 투자 관련 뉴스가 언급됨.</t>
+          <t>임상 시험 디자인 공개 및 학회 발표 임박에 따른 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '원전']</t>
+          <t>['임상 시험', '학회', '외인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,86 +1384,86 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7800</v>
+        <v>51050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>+1.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="G11" t="n">
-        <v>138</v>
+        <v>636</v>
       </c>
       <c r="H11" t="n">
-        <v>0.52</v>
+        <v>38.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7690</v>
+        <v>50400</v>
       </c>
       <c r="K11" t="n">
-        <v>7670</v>
+        <v>50500</v>
       </c>
       <c r="L11" t="n">
-        <v>9170</v>
+        <v>51200</v>
       </c>
       <c r="M11" t="n">
-        <v>7450</v>
+        <v>49650</v>
       </c>
       <c r="N11" t="n">
-        <v>0.46</v>
+        <v>38.69</v>
       </c>
       <c r="O11" t="n">
-        <v>88107479415</v>
+        <v>77060534725</v>
       </c>
       <c r="P11" t="n">
-        <v>9170</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>3720</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>14000</v>
+        <v>-172000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>594억 공급 계약 및 포스코 관련 사업 내용이 언급되나, 유통 물량 부족과 급등락에 대한 우려도 존재함.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시 확인 및 이에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공급계약', '포스코', '유통물량']</t>
+          <t>['수주', '공시', '삼성']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,86 +1476,86 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51000</v>
+        <v>7770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>170</v>
+        <v>123</v>
       </c>
       <c r="F12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
-        <v>629</v>
+        <v>149</v>
       </c>
       <c r="H12" t="n">
-        <v>38.78</v>
+        <v>0.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>50400</v>
+        <v>7690</v>
       </c>
       <c r="K12" t="n">
-        <v>50500</v>
+        <v>7670</v>
       </c>
       <c r="L12" t="n">
-        <v>51200</v>
+        <v>9170</v>
       </c>
       <c r="M12" t="n">
-        <v>49650</v>
+        <v>7450</v>
       </c>
       <c r="N12" t="n">
-        <v>38.69</v>
+        <v>0.46</v>
       </c>
       <c r="O12" t="n">
-        <v>74338188975</v>
+        <v>88518440990</v>
       </c>
       <c r="P12" t="n">
-        <v>67300</v>
+        <v>9170</v>
       </c>
       <c r="Q12" t="n">
-        <v>23150</v>
+        <v>3720</v>
       </c>
       <c r="R12" t="n">
-        <v>-172000</v>
+        <v>14000</v>
       </c>
       <c r="S12" t="n">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대형 수주 공시가 확인되었으며, 이에 따른 주가 상승 기대감이 높음.</t>
+          <t>주가 하락 및 거래량 부진에 대한 불안감. 594억 공급 계약 관련 사실 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '공시']</t>
+          <t>['주가 하락', '거래량', '공급 계약']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52300</v>
+        <v>19890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.44</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
+        <v>163</v>
+      </c>
+      <c r="F13" t="n">
         <v>92</v>
       </c>
-      <c r="F13" t="n">
-        <v>48</v>
-      </c>
       <c r="G13" t="n">
-        <v>201</v>
+        <v>574</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>10.65</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,130 +1607,130 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>51800</v>
+        <v>19750</v>
       </c>
       <c r="K13" t="n">
-        <v>51300</v>
+        <v>19500</v>
       </c>
       <c r="L13" t="n">
-        <v>54500</v>
+        <v>20150</v>
       </c>
       <c r="M13" t="n">
-        <v>51300</v>
+        <v>19060</v>
       </c>
       <c r="N13" t="n">
-        <v>3.36</v>
+        <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>103842912100</v>
+        <v>131783140830</v>
       </c>
       <c r="P13" t="n">
-        <v>87700</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>127000</v>
+        <v>28000</v>
       </c>
       <c r="S13" t="n">
-        <v>34000</v>
+        <v>-43000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>대차해지 요청과 함께 공매도 관련 논의가 활발하며, 목표가 상향 및 원전 투자 관련 뉴스가 언급됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['대차해지', '공매도', '원전']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26350</v>
+        <v>52100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.01</v>
+        <v>-0.44</v>
       </c>
       <c r="E14" t="n">
-        <v>342</v>
+        <v>95</v>
       </c>
       <c r="F14" t="n">
-        <v>164</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>540</v>
+        <v>204</v>
       </c>
       <c r="H14" t="n">
-        <v>0.32</v>
+        <v>2.92</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>26100</v>
+        <v>51800</v>
       </c>
       <c r="K14" t="n">
-        <v>26350</v>
+        <v>51300</v>
       </c>
       <c r="L14" t="n">
-        <v>30300</v>
+        <v>54500</v>
       </c>
       <c r="M14" t="n">
-        <v>25400</v>
+        <v>51300</v>
       </c>
       <c r="N14" t="n">
-        <v>0.33</v>
+        <v>3.36</v>
       </c>
       <c r="O14" t="n">
-        <v>334161249225</v>
+        <v>105500927750</v>
       </c>
       <c r="P14" t="n">
-        <v>39350</v>
+        <v>87700</v>
       </c>
       <c r="Q14" t="n">
-        <v>8200</v>
+        <v>17210</v>
       </c>
       <c r="R14" t="n">
-        <v>2000</v>
+        <v>127000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 부정적 심리가 강하며, 명확한 사실 기반 분석은 부족함.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,51 +1739,51 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90700</v>
+        <v>415500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>0.2</v>
       </c>
       <c r="E15" t="n">
-        <v>244</v>
+        <v>113</v>
       </c>
       <c r="F15" t="n">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>950</v>
+        <v>301</v>
       </c>
       <c r="H15" t="n">
-        <v>23.59</v>
+        <v>38.02</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,143 +1791,143 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>89900</v>
+        <v>417500</v>
       </c>
       <c r="K15" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>91000</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>23.65</v>
+        <v>37.82</v>
       </c>
       <c r="O15" t="n">
-        <v>175969670750</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-313000</v>
+        <v>31000</v>
       </c>
       <c r="S15" t="n">
-        <v>77000</v>
+        <v>5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 29조 7천억 규모 기반 상승 기대.</t>
+          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['에너지', '수주잔고', '원전']</t>
+          <t>['수주', '로봇', '미래차']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1899</v>
+        <v>25900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E16" t="n">
+        <v>354</v>
+      </c>
+      <c r="F16" t="n">
+        <v>169</v>
+      </c>
+      <c r="G16" t="n">
+        <v>549</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.32</v>
       </c>
-      <c r="E16" t="n">
-        <v>130</v>
-      </c>
-      <c r="F16" t="n">
-        <v>65</v>
-      </c>
-      <c r="G16" t="n">
-        <v>261</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.44</v>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1901</v>
+        <v>26100</v>
       </c>
       <c r="K16" t="n">
-        <v>2050</v>
+        <v>26350</v>
       </c>
       <c r="L16" t="n">
-        <v>2080</v>
+        <v>30300</v>
       </c>
       <c r="M16" t="n">
-        <v>1899</v>
+        <v>25400</v>
       </c>
       <c r="N16" t="n">
-        <v>2.12</v>
+        <v>0.33</v>
       </c>
       <c r="O16" t="n">
-        <v>43701509725</v>
+        <v>338688473000</v>
       </c>
       <c r="P16" t="n">
-        <v>4795</v>
+        <v>39350</v>
       </c>
       <c r="Q16" t="n">
-        <v>1524</v>
+        <v>8200</v>
       </c>
       <c r="R16" t="n">
-        <v>-445000</v>
+        <v>2000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 급등 관련 전쟁 테마주로 분류되며, VLCC 용선료 폭등 소식이 전해지고 있음.</t>
+          <t>주가 하락에 대한 부정적 심리가 강하며, 명확한 사실 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', 'VLCC', '유가']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>415000</v>
+        <v>29550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>291</v>
+        <v>174</v>
       </c>
       <c r="H17" t="n">
-        <v>38.02</v>
+        <v>25.55</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>415500</v>
+        <v>29800</v>
       </c>
       <c r="K17" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>418000</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>37.82</v>
+        <v>24.99</v>
       </c>
       <c r="O17" t="n">
-        <v>63849951500</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>31000</v>
+        <v>599000</v>
       </c>
       <c r="S17" t="n">
-        <v>5000</v>
+        <v>-270000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['수주', '로봇', '미래차']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3910</v>
+        <v>3885</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2082,7 +2082,7 @@
         <v>1.57</v>
       </c>
       <c r="O18" t="n">
-        <v>95273906583</v>
+        <v>95901728635</v>
       </c>
       <c r="P18" t="n">
         <v>8100</v>
@@ -2091,10 +2091,10 @@
         <v>592</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-560000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29550</v>
+        <v>8870</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E19" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>171</v>
+        <v>293</v>
       </c>
       <c r="H19" t="n">
-        <v>25.55</v>
+        <v>27.19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>29800</v>
+        <v>8970</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>8780</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>8890</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>8680</v>
       </c>
       <c r="N19" t="n">
-        <v>24.99</v>
+        <v>27.16</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>19325812140</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>599000</v>
+        <v>-8000</v>
       </c>
       <c r="S19" t="n">
-        <v>-270000</v>
+        <v>-241000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8880</v>
+        <v>14850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>290</v>
+        <v>331</v>
       </c>
       <c r="H20" t="n">
-        <v>27.19</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8970</v>
+        <v>15040</v>
       </c>
       <c r="K20" t="n">
-        <v>8780</v>
+        <v>14550</v>
       </c>
       <c r="L20" t="n">
-        <v>8890</v>
+        <v>15260</v>
       </c>
       <c r="M20" t="n">
-        <v>8680</v>
+        <v>14350</v>
       </c>
       <c r="N20" t="n">
-        <v>27.16</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>18938907965</v>
+        <v>23356269755</v>
       </c>
       <c r="P20" t="n">
-        <v>17950</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>8120</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>-8000</v>
+        <v>23000</v>
       </c>
       <c r="S20" t="n">
-        <v>-241000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['경영부진', '주가하락', '디스플레이']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14820</v>
+        <v>89900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E21" t="n">
-        <v>92</v>
+        <v>247</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="G21" t="n">
-        <v>317</v>
+        <v>958</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>23.59</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,91 +2343,91 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15040</v>
+        <v>91700</v>
       </c>
       <c r="K21" t="n">
-        <v>14550</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>15260</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>14350</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="O21" t="n">
-        <v>21908447530</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>19380</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>23000</v>
+        <v>-313000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
+          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 29조 7천억 규모 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
+          <t>['에너지', '수주잔고', '원전']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1803000</v>
+        <v>192900</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.86%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>94</v>
       </c>
       <c r="F22" t="n">
-        <v>445</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>2066</v>
+        <v>165</v>
       </c>
       <c r="H22" t="n">
-        <v>50.55</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1856000</v>
+        <v>197500</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>50.67</v>
+        <v>75.92</v>
       </c>
       <c r="O22" t="n">
-        <v>3790074000000</v>
+        <v>513003000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2459,128 +2459,128 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-393000</v>
+        <v>-1193000</v>
       </c>
       <c r="S22" t="n">
-        <v>-178000</v>
+        <v>-48000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>중동 평화 회담 관련 호재와 함께 기관 매수세 유입, 상승 추세 지속 기대.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['중동', '기관 매수', '추세']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>비엘팜텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2095</v>
+        <v>1804000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.01%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="E23" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>448</v>
       </c>
       <c r="G23" t="n">
-        <v>397</v>
+        <v>2114</v>
       </c>
       <c r="H23" t="n">
-        <v>1.32</v>
+        <v>50.55</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2160</v>
+        <v>1853000</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1773000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1812000</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1768000</v>
       </c>
       <c r="N23" t="n">
-        <v>1.36</v>
+        <v>50.67</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3875028945000</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>305500</v>
       </c>
       <c r="R23" t="n">
-        <v>219000</v>
+        <v>-393000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-178000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
+          <t>중동 평화 회담 선언 및 유가 급락에 따른 영향. 계단식 상승 및 기관 매수세에 대한 기대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
+          <t>['중동 평화 회담', '유가 급락', '기관 매수']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>065170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>259500</v>
+        <v>259250</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>-3.62%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2608,7 +2608,7 @@
         <v>498</v>
       </c>
       <c r="G24" t="n">
-        <v>1793</v>
+        <v>1755</v>
       </c>
       <c r="H24" t="n">
         <v>46.71</v>
@@ -2634,7 +2634,7 @@
         <v>46.81</v>
       </c>
       <c r="O24" t="n">
-        <v>2870071698000</v>
+        <v>2952657484750</v>
       </c>
       <c r="P24" t="n">
         <v>374500</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>이재명 재판 관련 정치적 요인과 반도체 시장 상황이 주가에 영향을 미칠 것이라는 의견이 있으나, 구체적인 근거는 부족함.</t>
+          <t>정치적 이슈와 증권 시장 전반에 대한 부정적 인식. 반도체 업황 및 개별 종목 주가 변동성에 대한 불만.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '주가']</t>
+          <t>['정치적 이슈', '반도체 업황', '주가 변동성']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2679,83 +2679,83 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14150</v>
+        <v>7375</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.00%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.39</v>
+        <v>0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="F25" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G25" t="n">
-        <v>443</v>
+        <v>506</v>
       </c>
       <c r="H25" t="n">
-        <v>2.5</v>
+        <v>11.72</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>14740</v>
+        <v>7680</v>
       </c>
       <c r="K25" t="n">
-        <v>14050</v>
+        <v>7540</v>
       </c>
       <c r="L25" t="n">
-        <v>14560</v>
+        <v>7660</v>
       </c>
       <c r="M25" t="n">
-        <v>14030</v>
+        <v>7340</v>
       </c>
       <c r="N25" t="n">
-        <v>2.89</v>
+        <v>11.62</v>
       </c>
       <c r="O25" t="n">
-        <v>63203703155</v>
+        <v>11443188345</v>
       </c>
       <c r="P25" t="n">
-        <v>31500</v>
+        <v>8850</v>
       </c>
       <c r="Q25" t="n">
-        <v>1272</v>
+        <v>4220</v>
       </c>
       <c r="R25" t="n">
-        <v>-303000</v>
+        <v>45000</v>
       </c>
       <c r="S25" t="n">
-        <v>-28000</v>
+        <v>1000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>정치적 요인과 금리 인상 관련 언급이 있으며, 우리로 종목과의 비교 및 매수 기회에 대한 논의가 있음.</t>
+          <t>뉴스 기반 주가 상승 기대와 함께 개인 투자자의 자금 이탈 및 기관 매수 가능성에 대한 언급이 혼재되어 있음.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['정치', '금리', '매수']</t>
+          <t>['주가 상승', '기관 매수', '개인 투자자']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,38 +2764,38 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12100</v>
+        <v>14150</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-4.20%</t>
+          <t>-4.00%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>-0.39</v>
       </c>
       <c r="E26" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F26" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G26" t="n">
-        <v>116</v>
+        <v>443</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,60 +2803,60 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12630</v>
+        <v>14740</v>
       </c>
       <c r="K26" t="n">
-        <v>12520</v>
+        <v>14050</v>
       </c>
       <c r="L26" t="n">
-        <v>12930</v>
+        <v>14560</v>
       </c>
       <c r="M26" t="n">
-        <v>12010</v>
+        <v>14030</v>
       </c>
       <c r="N26" t="n">
-        <v>0.14</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
-        <v>64539238140</v>
+        <v>64290753735</v>
       </c>
       <c r="P26" t="n">
-        <v>20850</v>
+        <v>31500</v>
       </c>
       <c r="Q26" t="n">
-        <v>4020</v>
+        <v>1272</v>
       </c>
       <c r="R26" t="n">
-        <v>-105000</v>
+        <v>-303000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-28000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
+          <t>정치적 요인과 금리 인상 관련 언급이 있으며, 우리로 종목과의 비교 및 매수 기회에 대한 논의가 있음.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '거래량']</t>
+          <t>['정치', '금리', '매수']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2878,13 +2878,13 @@
         <v>-0.11</v>
       </c>
       <c r="E27" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F27" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G27" t="n">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="H27" t="n">
         <v>5.98</v>
@@ -2910,7 +2910,7 @@
         <v>6.09</v>
       </c>
       <c r="O27" t="n">
-        <v>113761926805</v>
+        <v>115189477455</v>
       </c>
       <c r="P27" t="n">
         <v>30200</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>원전 관련 이슈 속 모건 스탠리 매도 물량 출회, 단기 과열 가능성 언급.</t>
+          <t>원전 관련 언급과 함께 일부 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['원전', '모건스탠리']</t>
+          <t>['원전', '매수세', '120일선']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2955,31 +2955,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7910</v>
+        <v>9280</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-4.70%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>257</v>
+        <v>76</v>
       </c>
       <c r="F28" t="n">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="G28" t="n">
-        <v>1261</v>
+        <v>335</v>
       </c>
       <c r="H28" t="n">
-        <v>1.29</v>
+        <v>4.49</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2987,130 +2987,130 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>8300</v>
+        <v>9800</v>
       </c>
       <c r="K28" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>7540</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.17</v>
+        <v>4.42</v>
       </c>
       <c r="O28" t="n">
-        <v>30489422015</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-183000</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>9월 14일 WCLC 학회 센딥파텔 교수 데이터 발표 기반 주가 대폭등 예고.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['WCLC', '폐암학회', '데이터']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>193100</v>
+        <v>12020</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-4.88%</t>
+          <t>-7.75%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="F29" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G29" t="n">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="H29" t="n">
-        <v>75.98999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>203000</v>
+        <v>13030</v>
       </c>
       <c r="K29" t="n">
-        <v>195000</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>195600</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>191000</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>75.92</v>
+        <v>0.14</v>
       </c>
       <c r="O29" t="n">
-        <v>504003529650</v>
+        <v>65204000000</v>
       </c>
       <c r="P29" t="n">
-        <v>243500</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>-1193000</v>
+        <v>-105000</v>
       </c>
       <c r="S29" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
@@ -3119,11 +3119,11 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -3154,13 +3154,13 @@
         <v>-0.96</v>
       </c>
       <c r="E30" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F30" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G30" t="n">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="H30" t="n">
         <v>7.58</v>
@@ -3186,7 +3186,7 @@
         <v>8.539999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>213485181500</v>
+        <v>218418713250</v>
       </c>
       <c r="P30" t="n">
         <v>426000</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>9월 TC본더 수출 데이터 및 공매도 관련 논의가 활발하며, 주가 하락에 대한 우려와 함께 기관 매수세가 언급됨.</t>
+          <t>공매도 세력과의 공방이 치열한 가운데, 주가 하락에 대한 우려와 함께 매수 후 소각 등 주주 가치 제고 방안에 대한 요구가 나타나고 있음.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['TC본더', '공매도', '기관']</t>
+          <t>['공매도', '주가 하락', '매수 소각']</t>
         </is>
       </c>
       <c r="X30" t="n">
@@ -3246,13 +3246,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F31" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H31" t="n">
         <v>0.73</v>
@@ -3278,7 +3278,7 @@
         <v>1.54</v>
       </c>
       <c r="O31" t="n">
-        <v>48216000000</v>
+        <v>48432000000</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>-110000</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
